--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>리와인드 휘트니스 일산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>rewind9089@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1414-2729</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://linktr.ee/junistar3579</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,18 +601,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45mlf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1176</v>
+        <v>338</v>
       </c>
       <c r="Q2" t="n">
-        <v>874</v>
+        <v>202</v>
       </c>
       <c r="R2" t="n">
-        <v>2050</v>
+        <v>540</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1294694330</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1294694330</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>휘트니스칸 헬스&amp;PT&amp;요가&amp;필라테스 주엽점</t>
+          <t>리와인드 휘트니스 중산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kann5555@naver.com</t>
+          <t>rewind_8990@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1396-3191</t>
+          <t>0507-1300-9146</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+          <t>경기 고양시 일산동구 고양대로 762 406~412호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://www.instagram.com/rewind_fitness2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u1uf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2037</v>
+        <v>167</v>
       </c>
       <c r="Q3" t="n">
-        <v>885</v>
+        <v>138</v>
       </c>
       <c r="R3" t="n">
-        <v>2922</v>
+        <v>305</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,24 +738,24 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1797149054</t>
+          <t>1726802714</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797149054</t>
+          <t>https://m.place.naver.com/place/1726802714</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9v3</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2376</v>
+        <v>2433</v>
       </c>
       <c r="Q4" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="R4" t="n">
-        <v>4398</v>
+        <v>4463</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,41 +846,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>핏포유 탄현점 헬스PT</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fit4u2019@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1363-6711</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
+          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -893,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dzwt</t>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4942</v>
+        <v>1221</v>
       </c>
       <c r="Q5" t="n">
-        <v>4952</v>
+        <v>1612</v>
       </c>
       <c r="R5" t="n">
-        <v>9894</v>
+        <v>2833</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,66 +934,66 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>60823193</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60823193</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kobygym@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1374-2418</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+          <t>경기 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -991,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we6ins2</t>
+          <t>https://talk.naver.com/ct/w4skng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1005,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1003</v>
+        <v>1186</v>
       </c>
       <c r="Q6" t="n">
-        <v>1004</v>
+        <v>804</v>
       </c>
       <c r="R6" t="n">
-        <v>2007</v>
+        <v>1990</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1332252606</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332252606</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>베르만짐 헬스&amp;PT 식사점</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>qpfmaks02@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-2708</t>
+          <t>0507-1373-7656</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1074,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1089,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjxd4y3</t>
+          <t>https://talk.naver.com/ct/w4dgq8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>681</v>
+        <v>615</v>
       </c>
       <c r="Q7" t="n">
-        <v>679</v>
+        <v>792</v>
       </c>
       <c r="R7" t="n">
-        <v>1360</v>
+        <v>1407</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,56 +1130,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1722963960</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722963960</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1187,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zymk</t>
+          <t>https://talk.naver.com/ct/wu9oxes</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>896</v>
+        <v>240</v>
       </c>
       <c r="Q8" t="n">
-        <v>895</v>
+        <v>438</v>
       </c>
       <c r="R8" t="n">
-        <v>1791</v>
+        <v>678</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>berman_gym@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1483-3436</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
+          <t>경기 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,12 +1282,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wvt0jtv</t>
+          <t>https://talk.naver.com/ct/w461vb</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1299,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1549</v>
+        <v>671</v>
       </c>
       <c r="Q9" t="n">
-        <v>1550</v>
+        <v>1047</v>
       </c>
       <c r="R9" t="n">
-        <v>3099</v>
+        <v>1718</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,78 +1326,74 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1924109138</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924109138</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>고포잇짐 헬스&amp;PT 장항점</t>
+          <t>머스타드피트니스 운정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>go4itgym1@naver.com</t>
+          <t>mustard_fitness3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1315-5550</t>
+          <t>0507-1403-6882</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.mustard-fitness.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4i1nr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>784</v>
+        <v>1041</v>
       </c>
       <c r="Q10" t="n">
-        <v>777</v>
+        <v>123</v>
       </c>
       <c r="R10" t="n">
-        <v>1561</v>
+        <v>1164</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1738952122</t>
+          <t>584588992</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738952122</t>
+          <t>https://m.place.naver.com/place/584588992</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1434,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>에이플러스짐 PT 중산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
+          <t>aplusgym600@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>031-977-5755</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://blog.naver.com/aplusgym600/222983159417</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dgq8</t>
+          <t>https://talk.naver.com/ct/w2t1k29</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>792</v>
+        <v>490</v>
       </c>
       <c r="Q11" t="n">
-        <v>792</v>
+        <v>740</v>
       </c>
       <c r="R11" t="n">
-        <v>1584</v>
+        <v>1230</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>1426431657</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/1426431657</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1532,29 +1540,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1564,12 +1572,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1579,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w461vb</t>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1593,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1026</v>
+        <v>1346</v>
       </c>
       <c r="Q12" t="n">
-        <v>1026</v>
+        <v>327</v>
       </c>
       <c r="R12" t="n">
-        <v>2052</v>
+        <v>1673</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1630,34 +1638,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>olof7l6h@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1431-9036</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
+          <t>경기 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/forestgym_2</t>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1667,7 +1675,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1677,7 +1685,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yfab</t>
+          <t>https://talk.naver.com/ct/w5tj13</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1691,13 +1699,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>531</v>
+        <v>1242</v>
       </c>
       <c r="Q13" t="n">
-        <v>531</v>
+        <v>1085</v>
       </c>
       <c r="R13" t="n">
-        <v>1062</v>
+        <v>2327</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1706,785 +1714,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1320621577</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320621577</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>버클다운짐 탄현점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>buckledown1234@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1358-3972</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1228</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1082</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2310</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1918164834</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>투게더휘트니스 일산점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>togetherfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1461-1485</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>289</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>293</v>
-      </c>
-      <c r="R15" t="n">
-        <v>582</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1161506645</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5150피트니스 일산 대화점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5150fitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1348-8027</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1612</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1612</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3224</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1817673935</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>스포애니 마두역점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>spoany64@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1369-7697</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h0gc</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2183</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2184</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4367</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1639489562</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1639489562</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>짐박스피트니스 탄현제니스점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1458-0638</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>33</v>
-      </c>
-      <c r="R18" t="n">
-        <v>66</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2038926940</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>식스틴 휘트니스</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>sixteen_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 성석로 7 2층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>173</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>430</v>
-      </c>
-      <c r="R19" t="n">
-        <v>603</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1004973811</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1004973811</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>맥스아웃휘트니스 정발산점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>maxoutfitness_1@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1376-9699</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 19 호수광장빌딩 9층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4923f</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>649</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>649</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1298</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>35287626</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/35287626</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>플렉스짐 백석점 PT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>flexgym_baekseok@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>332</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>332</v>
-      </c>
-      <c r="R21" t="n">
-        <v>664</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1742139437</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1742139437</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -628,10 +628,10 @@
         <v>338</v>
       </c>
       <c r="Q2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R2" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u1uf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u9v3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2433</v>
+        <v>2439</v>
       </c>
       <c r="Q4" t="n">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="R4" t="n">
-        <v>4463</v>
+        <v>4471</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -875,12 +867,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +882,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -944,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,34 +948,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1373-7656</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4skng</t>
+          <t>https://talk.naver.com/ct/w4dgq8</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1186</v>
+        <v>615</v>
       </c>
       <c r="Q6" t="n">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="R6" t="n">
-        <v>1990</v>
+        <v>1407</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1046,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dgq8</t>
+          <t>https://talk.naver.com/ct/w4skng</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>615</v>
+        <v>1187</v>
       </c>
       <c r="Q7" t="n">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="R7" t="n">
-        <v>1407</v>
+        <v>1991</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>kann5555@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1445-5805</t>
+          <t>0507-1396-3191</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,12 +1176,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1191,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wu9oxes</t>
+          <t>https://talk.naver.com/ct/w41bm5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>240</v>
+        <v>2042</v>
       </c>
       <c r="Q8" t="n">
-        <v>438</v>
+        <v>906</v>
       </c>
       <c r="R8" t="n">
-        <v>678</v>
+        <v>2948</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>1797149054</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/1797149054</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>에이치짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>ssj783312@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>031-943-0116</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/readybody2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,27 +1274,23 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w461vb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>671</v>
+        <v>367</v>
       </c>
       <c r="Q9" t="n">
-        <v>1047</v>
+        <v>420</v>
       </c>
       <c r="R9" t="n">
-        <v>1718</v>
+        <v>787</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>548127191</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/548127191</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1390,10 +1378,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5itt3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="Q10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R10" t="n">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1430,41 +1422,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이플러스짐 PT 중산점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>aplusgym600@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-977-5755</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym600/222983159417</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,12 +1466,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2t1k29</t>
+          <t>https://talk.naver.com/ct/w42s1j</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>490</v>
+        <v>304</v>
       </c>
       <c r="Q11" t="n">
-        <v>740</v>
+        <v>268</v>
       </c>
       <c r="R11" t="n">
-        <v>1230</v>
+        <v>572</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1426431657</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426431657</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1540,29 +1532,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>탑 메디컬 트레이닝&amp;pt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>woosc9090@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1303-3474</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1572,12 +1564,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1587,7 +1579,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
+          <t>https://talk.naver.com/ct/w4mk8a</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1346</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="R12" t="n">
-        <v>1673</v>
+        <v>112</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,115 +1608,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1747685925</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1747685925</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>버클다운짐 탄현점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>buckledown1234@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1358-3972</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기 고양시 일산서구 일현로 107 4층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1242</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1085</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2327</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1918164834</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기 고양시 일산동구 고양대로 762 406~412호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u1uf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9v3</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -867,12 +875,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -965,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1063,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1161,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+          <t>경기 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1208,10 +1216,10 @@
         <v>2042</v>
       </c>
       <c r="Q8" t="n">
-        <v>906</v>
+        <v>927</v>
       </c>
       <c r="R8" t="n">
-        <v>2948</v>
+        <v>2969</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1259,12 +1267,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hgym24/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1353,7 +1361,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
+          <t>경기 파주시 와석순환로 86 지앤지프라자 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1429,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,12 +1474,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42s1j</t>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>304</v>
+        <v>1353</v>
       </c>
       <c r="Q11" t="n">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="R11" t="n">
-        <v>572</v>
+        <v>1693</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,113 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>탑 메디컬 트레이닝&amp;pt</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>woosc9090@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1303-3474</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mk8a</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>83</v>
-      </c>
-      <c r="R12" t="n">
-        <v>112</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1747685925</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1747685925</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더핏퍼스널트레이닝</t>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sky_se@naver.com</t>
+          <t>momentfit100@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1411-0772</t>
+          <t>0507-1483-9679</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sky_se/223038038455</t>
+          <t>http://pf.kakao.com/_xkxdCus</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,30 +715,6880 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>582</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>841</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1423</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1147827351</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147827351</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 마두점</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>respect1333@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1335-1380</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/respect1333</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1392</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2767</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1420492815</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1420492815</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>플렉스짐 백석점 PT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>flexgym_baekseok@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1361-3798</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/flexgym_baekseok</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>334</v>
+      </c>
+      <c r="R5" t="n">
+        <v>565</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1742139437</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742139437</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>developfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1374-2418</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/developfitness</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>708</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1713</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1332252606</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332252606</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1986피트니스 헬스PT 24시 중산점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1986fitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 244 6층</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/1986fitness3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1305</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1290</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2595</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1052772360</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1052772360</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>디노짐 헬스PT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dinogym2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1341-5664</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dinogym2023</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>448</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>252</v>
+      </c>
+      <c r="R8" t="n">
+        <v>700</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1693675710</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693675710</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>고포잇짐 헬스&amp;PT 장항점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>go4itgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1315-5550</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/go4itgym1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>712</v>
+      </c>
+      <c r="R9" t="n">
+        <v>875</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1738952122</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1738952122</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>크로스핏ATD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bebetters@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1352-5696</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주화로 210 우리프라자 B1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/cfatd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>46</v>
+      </c>
+      <c r="R10" t="n">
+        <v>61</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1758813134</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758813134</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>테디케이짐 헬스 PT 풍동점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>imka121@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1483-6336</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/imka121</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>537</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>256</v>
+      </c>
+      <c r="R11" t="n">
+        <v>793</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1011101134</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011101134</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 탄현제니스점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1458-0638</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=80</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>754</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>33</v>
+      </c>
+      <c r="R12" t="n">
+        <v>787</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2038926940</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038926940</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>베르만짐 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>qpfmaks02@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1349-2708</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhhtNn</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>669</v>
+      </c>
+      <c r="R13" t="n">
+        <v>992</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1722963960</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1722963960</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>휘트니스바로 중산점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fitnessbaro@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1467-5222</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 67 아카메디건물 5층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/fitnessbaro</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>912</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>254</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1166</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1120920642</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1120920642</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 마두역점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>onfleekfitness1@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1367-9479</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 장백로 178 3층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onfleekfitness1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>508</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>190</v>
+      </c>
+      <c r="R15" t="n">
+        <v>698</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1196366994</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196366994</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>resort_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1434-4080</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/resort_13</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>561</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>929</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1490</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1379874016</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379874016</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>더스카이짐 중산마을점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>theskygym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1388-0593</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 탄중로 421 웅산프라자 지하1층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/theskygym3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>318</v>
+      </c>
+      <c r="R17" t="n">
+        <v>414</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1519762125</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1519762125</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>readybody2@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1359-9680</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/readybody2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>679</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1051</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1730</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>776760797</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/776760797</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>식스틴 휘트니스</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sixteen_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 성석로 7 2층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>461</v>
+      </c>
+      <c r="R19" t="n">
+        <v>638</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1004973811</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1004973811</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kann5555@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1396-3191</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://fitnesskann.com/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>2042</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>929</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2971</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1797149054</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1797149054</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>용구의 바디스토리</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>crazynael@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1461-9590</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-21 2층 204호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>51</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>21608242</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21608242</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>맥스아웃휘트니스 정발산점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>maxoutfitness_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1376-9699</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1261번길 19 호수광장빌딩 9층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxoutfitness__1/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1653</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>651</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2304</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>35287626</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35287626</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>에이플러스짐휘트니스센터 백마학원가점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>aplusgym500@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aplusgym500/223716202422</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>110</v>
+      </c>
+      <c r="R23" t="n">
+        <v>199</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2067321363</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067321363</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>크로스핏 GK 일산 마두점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>la40012@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1310-9524</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 113 지하1층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/cfgkmd</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>412</v>
+      </c>
+      <c r="R24" t="n">
+        <v>678</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1085090977</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1085090977</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 일산역점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>onfleek555@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1319-9498</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 경의로 665 501호, 502호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onfleek555</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>140</v>
+      </c>
+      <c r="R25" t="n">
+        <v>297</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1112352231</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1112352231</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>짐300</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>gym_300@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1376-6714</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 고양대로 666 지하1층 M111, 112, 114, 115호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gym_300/224211731704</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>310</v>
+      </c>
+      <c r="R26" t="n">
+        <v>609</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1408702037</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1408702037</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>더블에잇휘트니스덕이점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>double79988@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1346-7998</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 하이파크2로 40 금문프라자 7층 더블에잇휘트니스 덕이점</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/double79988</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>632</v>
+      </c>
+      <c r="R27" t="n">
+        <v>898</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1097065429</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1097065429</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>gymcare24@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1483-3436</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_elwnn</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>686</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1557</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2243</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1924109138</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1924109138</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>리와인드 휘트니스 중산점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rewind_8990@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1300-9146</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rewind_fitness2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>138</v>
+      </c>
+      <c r="R29" t="n">
+        <v>305</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1726802714</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726802714</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 주엽점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>onfleekfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1366-9479</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 7층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/13/bizes/1064744</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>172</v>
+      </c>
+      <c r="R30" t="n">
+        <v>438</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1142951221</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1142951221</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>가온 휘트니스 대화마을점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>gaonfitness_@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>031-919-6336</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 송포로 35 2층 202호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gaon_fitness_1?igsh=cTNodWxqdGMycWYy</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>980</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>368</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1348</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1693727202</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693727202</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>fitnessel_kintex@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1435-6332</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessel_kintex</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>315</v>
+      </c>
+      <c r="R32" t="n">
+        <v>520</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1678529668</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1678529668</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>gymonelab@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1328-9681</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>196</v>
+      </c>
+      <c r="R33" t="n">
+        <v>297</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1767374434</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1767374434</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>크로스핏 로얄 덕이점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>cfroyal@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1313-5230</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 덕이로 328-12 1층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sEr5lrYd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>205</v>
+      </c>
+      <c r="R34" t="n">
+        <v>224</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1498701834</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1498701834</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>actgym_02@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1445-5805</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>441</v>
+      </c>
+      <c r="R35" t="n">
+        <v>683</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1033726767</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1033726767</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>인프라짐 PT 대화역헬스장</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>infragym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1331-5665</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/infragym1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2439</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2032</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4471</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>11579499</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11579499</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>백석PT 짐플러스 휘트니스</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gymplus_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1370-0474</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1048 지하1층 짐플러스휘트니스</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymplus_fitness</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>65</v>
+      </c>
+      <c r="R37" t="n">
+        <v>145</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>38510579</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38510579</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>스포애니 마두역점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>spoany64@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1369-7697</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany64</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2210</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2698</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1639489562</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639489562</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5150피트니스 중산점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5150fitness5@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1370-4847</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 241 해태쇼핑타운 B1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/5150fitness5</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>406</v>
+      </c>
+      <c r="R39" t="n">
+        <v>755</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2006347781</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2006347781</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>더스카이짐 본점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>theskygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1481-6336</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 원일로 136 2층 더스카이짐</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/theskygym</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>306</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>466</v>
+      </c>
+      <c r="R40" t="n">
+        <v>772</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1360909658</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1360909658</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>범휘트니스 일산점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bum903@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1440-5101</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일중로 17 포오스프라자 5층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bum903</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>396</v>
+      </c>
+      <c r="R41" t="n">
+        <v>598</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>31590084</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31590084</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>핏포유 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>fit4u2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1363-6711</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fit4u2019</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>526</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5107</v>
+      </c>
+      <c r="R42" t="n">
+        <v>5633</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>60823193</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/60823193</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>리와인드 휘트니스 일산점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>rewind9089@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1414-2729</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/junistar3579</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>338</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>203</v>
+      </c>
+      <c r="R43" t="n">
+        <v>541</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1294694330</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1294694330</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>풍산휘트니스&amp;기구필라테스</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>psfitness_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>031-976-6911</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 풍산프라자 3층 전체</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/psfitness_pilates</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>559</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1034</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>38425785</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38425785</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>가온휘트니스 가좌 2호점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gaonfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1358-8077</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 송포로 261 101호 201호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gaonfitness2</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>259</v>
+      </c>
+      <c r="R45" t="n">
+        <v>340</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1261817011</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261817011</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>더블에잇휘트니스 마두점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>double7998@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1350-7998</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1171 현대프리젠트 9,10층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://partner.talk.naver.com/web/accounts/101675659/chat</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>735</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1022</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1951351429</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1951351429</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>범휘트니스 마두점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bummadu@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 328 지하층 101, 102, 103호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bumfitness.madu/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>108</v>
+      </c>
+      <c r="R47" t="n">
+        <v>491</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1200977920</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200977920</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>더스카이짐 정발산점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>theskygym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1491-4450</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 428 5층 더스카이짐 정발산점</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/theskygym2</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>179</v>
+      </c>
+      <c r="R48" t="n">
+        <v>247</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1311260923</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1311260923</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>healthboy67@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1373-7656</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/healthboygym67</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>615</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>792</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1407</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1251452457</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251452457</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>메인 휘트니스 후곡점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>main2211@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1484-2212</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 529 대화프라자 B동 지하1층 메인 휘트니스</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/main2211</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>286</v>
+      </c>
+      <c r="R50" t="n">
+        <v>486</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1308136724</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1308136724</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>툭짐</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ksm19088@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1313-1590</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1195 지1층 비101호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/took.gym</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>6</v>
+      </c>
+      <c r="R51" t="n">
+        <v>213</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2042000567</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2042000567</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>kann666@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1428-1174</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://fitnesskann.com/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1187</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>803</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1990</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1533278650</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1533278650</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>원잇핏 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>oneitfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1400-8861</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/oneitfit</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>594</v>
+      </c>
+      <c r="R53" t="n">
+        <v>823</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>13223584</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13223584</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/5150fitness2</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>1221</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1612</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2833</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1817673935</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817673935</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>maxoutfitness_3@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1378-6366</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxoutfitness__2/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1272</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>203</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1475</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1674766909</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674766909</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>바디에이원짐 헬스/PT/재활</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>art729@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1406-1457</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/art729/224075467295</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>335</v>
+      </c>
+      <c r="R56" t="n">
+        <v>877</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1241623010</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241623010</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lifetime1231@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1355-9897</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lifetime1231/223007274910</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>491</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1140</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1631</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1618140538</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618140538</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>범휘트니스 정발산점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jibum903@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1362-5111</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 432 5층 범휘트니스 정발산점</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jibum903</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>354</v>
+      </c>
+      <c r="R58" t="n">
+        <v>656</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1466459481</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466459481</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 백마역점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>onfleekfitness4@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1389-9498</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 경의로 315 지하1층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onfleekfitness4/</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>316</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>121</v>
+      </c>
+      <c r="R59" t="n">
+        <v>437</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1691525809</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691525809</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 대화점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>onfleek_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1382-6682</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1573 킨텍스프라자 9층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onfleek_fitness_/?igshid=MmIzYWVlNDQ5Yg%3D%3D</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>325</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>326</v>
+      </c>
+      <c r="R60" t="n">
+        <v>651</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1050985755</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1050985755</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>woduddl01@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1431-9036</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/forestgym_2</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yfab</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>852</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>535</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1387</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1320621577</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320621577</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>F45 일산</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>f45_ilsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 2층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/f45_ilsan</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>230</v>
+      </c>
+      <c r="R62" t="n">
+        <v>349</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1034749202</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034749202</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 백석점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>respect9696@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1431-9696</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/respectgym3</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>286</v>
+      </c>
+      <c r="R63" t="n">
+        <v>496</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1412423288</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412423288</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 탄현점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1321-3912</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 65 동현빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fpeoplew1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>903</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1217</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2120</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1845503473</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845503473</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>범휘트니스 풍동점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>bumfitness6@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1441-7530</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을1로 29-37 201호, 202호, 203호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bumfitness6/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>148</v>
+      </c>
+      <c r="R65" t="n">
+        <v>437</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1604516167</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1604516167</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>메인 휘트니스 백마학원가점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>main_bacma@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1489-2272</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강촌로 157 서울코아 비층 비01호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/main_bacma</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>157</v>
+      </c>
+      <c r="R66" t="n">
+        <v>342</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1057482007</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057482007</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>제이앤제이 피트니스 헬스&amp;PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>likegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1314-9695</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 2층 제이앤제이 피트니스</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jnjfitness_madu</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>303</v>
+      </c>
+      <c r="R67" t="n">
+        <v>753</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1181142706</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181142706</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>헬로우짐 헬스&amp;PT 백석점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>hellogym001@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1383-8244</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hellogym001</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>220</v>
+      </c>
+      <c r="R68" t="n">
+        <v>320</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1528105437</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1528105437</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>프라임핏 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>primefit_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>031-962-2306</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/prime_fit1/?igshid=MWpldjY4Y3h2dDF4ag%3D%3D</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1127</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>289</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1416</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1328418362</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1328418362</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>플렉스짐</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>flexgymilsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1401-3798</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 고봉로 32-19 남정씨티프라자7차 2층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/flexgym_ilsan</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>868</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1191</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>36615589</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36615589</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>더핏퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sky_se@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1411-0772</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sky_se/223038038455</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
         <v>181</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q71" t="n">
         <v>1127</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R71" t="n">
         <v>1308</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
         <is>
           <t>1707178271</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1707178271</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>bodyoffgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1381-8260</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyoffgym</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>510</v>
+      </c>
+      <c r="R72" t="n">
+        <v>643</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>32507674</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32507674</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>헌드레드짐 파주운정점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>hundredgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1327-5413</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/donghyeok_hundredgym/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>528</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>203</v>
+      </c>
+      <c r="R73" t="n">
+        <v>731</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1101743632</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101743632</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>투게더휘트니스 일산점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>togetherfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1461-1485</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/togetherfitness</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1353</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>341</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1694</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1161506645</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161506645</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>저스트플레잉</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>justplaying@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>031-965-1106</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>http://justplaying.co.kr/</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>407</v>
+      </c>
+      <c r="R75" t="n">
+        <v>534</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>37452748</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37452748</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>버클다운짐 탄현점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>buckledown1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1358-3972</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1089</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2339</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1918164834</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1918164834</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MTO 피트니스 PT 정발산점</t>
+          <t>고포잇짐 헬스&amp;PT 장항점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jbsfitness@naver.com</t>
+          <t>go4itgym1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1467-8389</t>
+          <t>0507-1315-5550</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
+          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jbsfitness</t>
+          <t>https://blog.naver.com/go4itgym1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>429</v>
+        <v>164</v>
       </c>
       <c r="Q2" t="n">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="R2" t="n">
-        <v>1157</v>
+        <v>876</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1314564243</t>
+          <t>1738952122</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314564243</t>
+          <t>https://m.place.naver.com/place/1738952122</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,44 +653,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모멘핏 헬스&amp;PT 식사점</t>
+          <t>가온휘트니스 가좌 2호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>momentfit100@naver.com</t>
+          <t>gaonfitness2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1483-9679</t>
+          <t>0507-1358-8077</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기도 고양시 일산서구 송포로 261 101호 201호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxdCus</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,13 +700,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wo6w86q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>582</v>
+        <v>81</v>
       </c>
       <c r="Q3" t="n">
-        <v>841</v>
+        <v>259</v>
       </c>
       <c r="R3" t="n">
-        <v>1423</v>
+        <v>340</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1147827351</t>
+          <t>1261817011</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147827351</t>
+          <t>https://m.place.naver.com/place/1261817011</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +751,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리스펙짐 PT 마두점</t>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>respect1333@naver.com</t>
+          <t>gymone10@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1335-1380</t>
+          <t>0507-1328-9681</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/respect1333</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfhd51g</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,17 +813,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1375</v>
+        <v>101</v>
       </c>
       <c r="Q4" t="n">
-        <v>1392</v>
+        <v>196</v>
       </c>
       <c r="R4" t="n">
-        <v>2767</v>
+        <v>297</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1420492815</t>
+          <t>1767374434</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420492815</t>
+          <t>https://m.place.naver.com/place/1767374434</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>플렉스짐 백석점 PT</t>
+          <t>툭짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flexgym_baekseok@naver.com</t>
+          <t>ksm19088@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1361-3798</t>
+          <t>0507-1313-1590</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
+          <t>경기도 고양시 일산동구 중앙로 1195 지1층 비101호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flexgym_baekseok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +886,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wb3igv3</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="Q5" t="n">
-        <v>334</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>565</v>
+        <v>213</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1742139437</t>
+          <t>2042000567</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742139437</t>
+          <t>https://m.place.naver.com/place/2042000567</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+          <t>메인 휘트니스 후곡점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>developfitness@naver.com</t>
+          <t>main2211@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1374-2418</t>
+          <t>0507-1484-2212</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+          <t>경기도 고양시 일산서구 일산로 529 대화프라자 B동 지하1층 메인 휘트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/developfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +984,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4x9on</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>708</v>
+        <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>1005</v>
+        <v>286</v>
       </c>
       <c r="R6" t="n">
-        <v>1713</v>
+        <v>486</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1332252606</t>
+          <t>1308136724</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332252606</t>
+          <t>https://m.place.naver.com/place/1308136724</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,25 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 24시 중산점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1986fitness3@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 244 6층</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness3</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1305</v>
+        <v>1221</v>
       </c>
       <c r="Q7" t="n">
-        <v>1290</v>
+        <v>1612</v>
       </c>
       <c r="R7" t="n">
-        <v>2595</v>
+        <v>2833</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1052772360</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1052772360</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>디노짐 헬스PT</t>
+          <t>더스카이짐 중산마을점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dinogym2023@naver.com</t>
+          <t>theskygym3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-5664</t>
+          <t>0507-1388-0593</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
+          <t>경기도 고양시 일산동구 탄중로 421 웅산프라자 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dinogym2023</t>
+          <t>https://blog.naver.com/theskygym3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,17 +1197,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>448</v>
+        <v>96</v>
       </c>
       <c r="Q8" t="n">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="R8" t="n">
-        <v>700</v>
+        <v>414</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1693675710</t>
+          <t>1519762125</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693675710</t>
+          <t>https://m.place.naver.com/place/1519762125</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1213,34 +1233,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>고포잇짐 헬스&amp;PT 장항점</t>
+          <t>온플릭휘트니스 주엽점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>go4itgym1@naver.com</t>
+          <t>onfleekfitness2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1315-5550</t>
+          <t>0507-1366-9479</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/go4itgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,20 +1270,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wqcn</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="Q9" t="n">
-        <v>712</v>
+        <v>172</v>
       </c>
       <c r="R9" t="n">
-        <v>875</v>
+        <v>438</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1738952122</t>
+          <t>1142951221</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738952122</t>
+          <t>https://m.place.naver.com/place/1142951221</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1307,34 +1331,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>크로스핏ATD</t>
+          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bebetters@naver.com</t>
+          <t>lifetime1231@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-5696</t>
+          <t>0507-1355-9897</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주화로 210 우리프라자 B1</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/cfatd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,23 +1368,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsf5729</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>491</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>1140</v>
       </c>
       <c r="R10" t="n">
-        <v>61</v>
+        <v>1631</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1758813134</t>
+          <t>1618140538</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758813134</t>
+          <t>https://m.place.naver.com/place/1618140538</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>테디케이짐 헬스 PT 풍동점</t>
+          <t>플렉스짐 백석점 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>imka121@naver.com</t>
+          <t>flexgym_baekseok@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1483-6336</t>
+          <t>0507-1361-3798</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/imka121</t>
+          <t>https://blog.naver.com/flexgym_baekseok</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>537</v>
+        <v>231</v>
       </c>
       <c r="Q11" t="n">
-        <v>256</v>
+        <v>334</v>
       </c>
       <c r="R11" t="n">
-        <v>793</v>
+        <v>565</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1506,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1011101134</t>
+          <t>1742139437</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011101134</t>
+          <t>https://m.place.naver.com/place/1742139437</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,38 +1528,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>짐박스피트니스 탄현제니스점</t>
+          <t>백석PT 짐플러스 휘트니스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>gymplus_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1458-0638</t>
+          <t>0507-1370-0474</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 지하1층 짐플러스휘트니스</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
+          <t>https://blog.naver.com/gymplus_fitness</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1552,7 +1576,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1585,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>754</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="R12" t="n">
-        <v>787</v>
+        <v>145</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1600,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2038926940</t>
+          <t>38510579</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
+          <t>https://m.place.naver.com/place/38510579</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1598,34 +1622,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>베르만짐 헬스&amp;PT 식사점</t>
+          <t>인프라짐 PT 대화역헬스장</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>qpfmaks02@naver.com</t>
+          <t>infragym1@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1349-2708</t>
+          <t>0507-1331-5665</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhhtNn</t>
+          <t>https://blog.naver.com/infragym1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1635,7 +1659,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1655,13 +1679,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>323</v>
+        <v>2439</v>
       </c>
       <c r="Q13" t="n">
-        <v>669</v>
+        <v>2032</v>
       </c>
       <c r="R13" t="n">
-        <v>992</v>
+        <v>4471</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,12 +1694,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1722963960</t>
+          <t>11579499</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722963960</t>
+          <t>https://m.place.naver.com/place/11579499</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1692,29 +1716,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>휘트니스바로 중산점</t>
+          <t>에이플러스짐휘트니스센터 백마학원가점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fitnessbaro@naver.com</t>
+          <t>aplusgym500@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1467-5222</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 67 아카메디건물 5층</t>
+          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/fitnessbaro</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1724,7 +1744,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1734,10 +1754,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl4apt8</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1749,13 +1773,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>912</v>
+        <v>89</v>
       </c>
       <c r="Q14" t="n">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="R14" t="n">
-        <v>1166</v>
+        <v>199</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,12 +1788,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1120920642</t>
+          <t>2067321363</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120920642</t>
+          <t>https://m.place.naver.com/place/2067321363</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1786,29 +1810,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>온플릭휘트니스 마두역점</t>
+          <t>5150피트니스 중산점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>onfleekfitness1@naver.com</t>
+          <t>5150fitness5@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1367-9479</t>
+          <t>0507-1370-4847</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 장백로 178 3층</t>
+          <t>경기도 고양시 일산동구 중산로 241 해태쇼핑타운 B1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onfleekfitness1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1818,20 +1842,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm84hjh</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1843,13 +1871,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>508</v>
+        <v>349</v>
       </c>
       <c r="Q15" t="n">
-        <v>190</v>
+        <v>406</v>
       </c>
       <c r="R15" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,12 +1886,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1196366994</t>
+          <t>2006347781</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1196366994</t>
+          <t>https://m.place.naver.com/place/2006347781</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1875,34 +1903,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>플렉스짐</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>flexgymilsan@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1401-3798</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기도 고양시 일산동구 고봉로 32-19 남정씨티프라자7차 2층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1912,12 +1940,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1937,13 +1965,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>561</v>
+        <v>323</v>
       </c>
       <c r="Q16" t="n">
-        <v>929</v>
+        <v>868</v>
       </c>
       <c r="R16" t="n">
-        <v>1490</v>
+        <v>1191</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,12 +1980,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>36615589</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/36615589</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1974,29 +2002,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>더스카이짐 중산마을점</t>
+          <t>더블에잇휘트니스덕이점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>theskygym3@naver.com</t>
+          <t>double79988@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1388-0593</t>
+          <t>0507-1346-7998</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 탄중로 421 웅산프라자 지하1층</t>
+          <t>경기도 고양시 일산서구 하이파크2로 40 금문프라자 7층 더블에잇휘트니스 덕이점</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theskygym3</t>
+          <t>https://blog.naver.com/double79988</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,17 +2055,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>96</v>
+        <v>266</v>
       </c>
       <c r="Q17" t="n">
-        <v>318</v>
+        <v>632</v>
       </c>
       <c r="R17" t="n">
-        <v>414</v>
+        <v>898</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,12 +2074,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1519762125</t>
+          <t>1097065429</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519762125</t>
+          <t>https://m.place.naver.com/place/1097065429</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2068,29 +2096,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>용구의 바디스토리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>park181809@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>0507-1461-9590</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-21 2층 204호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/readybody2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2100,20 +2128,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xxgn</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>X</t>
@@ -2121,17 +2153,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>679</v>
+        <v>26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1051</v>
+        <v>25</v>
       </c>
       <c r="R18" t="n">
-        <v>1730</v>
+        <v>51</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,12 +2172,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>21608242</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/21608242</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2162,25 +2194,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>식스틴 휘트니스</t>
+          <t>풍산휘트니스&amp;기구필라테스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sixteen_fitness@naver.com</t>
+          <t>psfitness_pilates@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>031-976-6911</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 성석로 7 2층</t>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 풍산프라자 3층 전체</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2190,7 +2226,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2200,10 +2236,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4688v</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2215,13 +2255,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>177</v>
+        <v>475</v>
       </c>
       <c r="Q19" t="n">
-        <v>461</v>
+        <v>560</v>
       </c>
       <c r="R19" t="n">
-        <v>638</v>
+        <v>1035</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,12 +2270,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1004973811</t>
+          <t>38425785</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004973811</t>
+          <t>https://m.place.naver.com/place/38425785</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2252,34 +2292,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>디노짐 헬스PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kann5555@naver.com</t>
+          <t>dinogym2023@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1396-3191</t>
+          <t>0507-1341-5664</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://blog.naver.com/dinogym2023</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2300,7 +2340,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2309,13 +2349,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2042</v>
+        <v>448</v>
       </c>
       <c r="Q20" t="n">
-        <v>929</v>
+        <v>252</v>
       </c>
       <c r="R20" t="n">
-        <v>2971</v>
+        <v>700</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,12 +2364,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1797149054</t>
+          <t>1693675710</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797149054</t>
+          <t>https://m.place.naver.com/place/1693675710</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2346,24 +2386,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>용구의 바디스토리</t>
+          <t>1986피트니스 헬스PT 24시 중산점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>crazynael@naver.com</t>
+          <t>1986fitness3@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1461-9590</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-21 2층 204호</t>
+          <t>경기도 고양시 일산동구 중산로 244 6층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2388,10 +2424,14 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40uu9</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>X</t>
@@ -2399,17 +2439,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>1305</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>1290</v>
       </c>
       <c r="R21" t="n">
-        <v>51</v>
+        <v>2595</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,12 +2458,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>21608242</t>
+          <t>1052772360</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21608242</t>
+          <t>https://m.place.naver.com/place/1052772360</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2435,34 +2475,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>맥스아웃휘트니스 정발산점</t>
+          <t>헬로우짐 헬스&amp;PT 백석점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>maxoutfitness_1@naver.com</t>
+          <t>hellogym001@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1376-9699</t>
+          <t>0507-1383-8244</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 19 호수광장빌딩 9층</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maxoutfitness__1/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2472,7 +2512,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2482,10 +2522,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cr18</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>X</t>
@@ -2497,13 +2541,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1653</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="n">
-        <v>651</v>
+        <v>220</v>
       </c>
       <c r="R22" t="n">
-        <v>2304</v>
+        <v>320</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,12 +2556,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>35287626</t>
+          <t>1528105437</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35287626</t>
+          <t>https://m.place.naver.com/place/1528105437</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2534,25 +2578,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에이플러스짐휘트니스센터 백마학원가점</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>aplusgym500@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1373-7656</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
+          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym500/223716202422</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2572,10 +2620,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dgq8</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2587,13 +2639,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>89</v>
+        <v>617</v>
       </c>
       <c r="Q23" t="n">
-        <v>110</v>
+        <v>792</v>
       </c>
       <c r="R23" t="n">
-        <v>199</v>
+        <v>1409</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,12 +2654,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2067321363</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067321363</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2619,34 +2671,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>크로스핏 GK 일산 마두점</t>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>la40012@naver.com</t>
+          <t>momentfit100@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1310-9524</t>
+          <t>0507-1483-9679</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 113 지하1층</t>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/cfgkmd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2656,23 +2708,27 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orzl</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2681,13 +2737,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>266</v>
+        <v>582</v>
       </c>
       <c r="Q24" t="n">
-        <v>412</v>
+        <v>841</v>
       </c>
       <c r="R24" t="n">
-        <v>678</v>
+        <v>1423</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,12 +2752,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1085090977</t>
+          <t>1147827351</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085090977</t>
+          <t>https://m.place.naver.com/place/1147827351</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2718,29 +2774,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>온플릭휘트니스 일산역점</t>
+          <t>크로스핏 로얄 덕이점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>onfleek555@naver.com</t>
+          <t>cfroyal@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1319-9498</t>
+          <t>0507-1313-5230</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 경의로 665 501호, 502호</t>
+          <t>경기도 고양시 일산서구 덕이로 328-12 1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onfleek555</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2750,12 +2806,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2766,7 +2822,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2775,13 +2831,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Q25" t="n">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="R25" t="n">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,12 +2846,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1112352231</t>
+          <t>1498701834</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1112352231</t>
+          <t>https://m.place.naver.com/place/1498701834</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2812,29 +2868,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>짐300</t>
+          <t>더블에잇휘트니스 마두점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>gym_300@naver.com</t>
+          <t>double7998@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1376-6714</t>
+          <t>0507-1350-7998</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 666 지하1층 M111, 112, 114, 115호</t>
+          <t>경기도 고양시 일산동구 중앙로 1171 현대프리젠트 9,10층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gym_300/224211731704</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2844,23 +2900,27 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48kl2</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2869,13 +2929,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="Q26" t="n">
-        <v>310</v>
+        <v>735</v>
       </c>
       <c r="R26" t="n">
-        <v>609</v>
+        <v>1022</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,12 +2944,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1408702037</t>
+          <t>1951351429</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1408702037</t>
+          <t>https://m.place.naver.com/place/1951351429</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2906,29 +2966,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>더블에잇휘트니스덕이점</t>
+          <t>테디케이짐 헬스 PT 풍동점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>double79988@naver.com</t>
+          <t>teddykgym@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1346-7998</t>
+          <t>0507-1483-6336</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 하이파크2로 40 금문프라자 7층 더블에잇휘트니스 덕이점</t>
+          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/double79988</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2938,20 +2998,24 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjaytn7</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>X</t>
@@ -2963,13 +3027,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>266</v>
+        <v>537</v>
       </c>
       <c r="Q27" t="n">
-        <v>632</v>
+        <v>256</v>
       </c>
       <c r="R27" t="n">
-        <v>898</v>
+        <v>793</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,12 +3042,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1097065429</t>
+          <t>1011101134</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097065429</t>
+          <t>https://m.place.naver.com/place/1011101134</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2995,44 +3059,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
+          <t>원잇핏 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gymcare24@naver.com</t>
+          <t>oneitfit@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1483-3436</t>
+          <t>0507-1400-8861</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
+          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_elwnn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3042,10 +3106,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eey</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>O</t>
@@ -3057,13 +3125,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>686</v>
+        <v>229</v>
       </c>
       <c r="Q28" t="n">
-        <v>1557</v>
+        <v>594</v>
       </c>
       <c r="R28" t="n">
-        <v>2243</v>
+        <v>823</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,12 +3140,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1924109138</t>
+          <t>13223584</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924109138</t>
+          <t>https://m.place.naver.com/place/13223584</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3094,29 +3162,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 중산점</t>
+          <t>더스카이짐 본점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rewind_8990@naver.com</t>
+          <t>theskygym@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1300-9146</t>
+          <t>0507-1481-6336</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기도 고양시 일산서구 원일로 136 2층 더스카이짐</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rewind_fitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3126,7 +3194,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3136,10 +3204,14 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4655z</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>X</t>
@@ -3151,13 +3223,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>167</v>
+        <v>306</v>
       </c>
       <c r="Q29" t="n">
-        <v>138</v>
+        <v>466</v>
       </c>
       <c r="R29" t="n">
-        <v>305</v>
+        <v>772</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,12 +3238,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1726802714</t>
+          <t>1360909658</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726802714</t>
+          <t>https://m.place.naver.com/place/1360909658</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3188,34 +3260,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>온플릭휘트니스 주엽점</t>
+          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>onfleekfitness2@naver.com</t>
+          <t>fitnessel_kintex@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1366-9479</t>
+          <t>0507-1435-6332</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 7층</t>
+          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/1064744</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3230,10 +3302,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yi1x</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3245,13 +3321,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="Q30" t="n">
-        <v>172</v>
+        <v>315</v>
       </c>
       <c r="R30" t="n">
-        <v>438</v>
+        <v>520</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,12 +3336,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1142951221</t>
+          <t>1678529668</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142951221</t>
+          <t>https://m.place.naver.com/place/1678529668</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3282,29 +3358,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>가온 휘트니스 대화마을점</t>
+          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gaonfitness_@naver.com</t>
+          <t>berman_gym@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>031-919-6336</t>
+          <t>0507-1483-3436</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 송포로 35 2층 202호</t>
+          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gaon_fitness_1?igsh=cTNodWxqdGMycWYy</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3314,7 +3390,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3324,13 +3400,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvt0jtv</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3339,13 +3419,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>980</v>
+        <v>687</v>
       </c>
       <c r="Q31" t="n">
-        <v>368</v>
+        <v>1557</v>
       </c>
       <c r="R31" t="n">
-        <v>1348</v>
+        <v>2244</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,12 +3434,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1693727202</t>
+          <t>1924109138</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693727202</t>
+          <t>https://m.place.naver.com/place/1924109138</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3376,29 +3456,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
+          <t>핏포유 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>fitnessel_kintex@naver.com</t>
+          <t>fit4u2019@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1435-6332</t>
+          <t>0507-1363-6711</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
+          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessel_kintex</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3408,20 +3488,24 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dzwt</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3433,13 +3517,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>205</v>
+        <v>526</v>
       </c>
       <c r="Q32" t="n">
-        <v>315</v>
+        <v>5107</v>
       </c>
       <c r="R32" t="n">
-        <v>520</v>
+        <v>5633</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,12 +3532,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1678529668</t>
+          <t>60823193</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678529668</t>
+          <t>https://m.place.naver.com/place/60823193</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3465,34 +3549,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+          <t>식스틴 휘트니스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>sixteen_fitness@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1328-9681</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기도 고양시 일산동구 성석로 7 2층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3502,20 +3582,24 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40gss</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>X</t>
@@ -3523,17 +3607,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="Q33" t="n">
-        <v>196</v>
+        <v>461</v>
       </c>
       <c r="R33" t="n">
-        <v>297</v>
+        <v>638</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,12 +3626,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1767374434</t>
+          <t>1004973811</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767374434</t>
+          <t>https://m.place.naver.com/place/1004973811</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3564,29 +3648,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>크로스핏 로얄 덕이점</t>
+          <t>맥스아웃휘트니스 정발산점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cfroyal@naver.com</t>
+          <t>maxoutfitness_1@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1313-5230</t>
+          <t>0507-1376-9699</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 덕이로 328-12 1층</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 19 호수광장빌딩 9층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sEr5lrYd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3596,7 +3680,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3606,13 +3690,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4923f</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3621,13 +3709,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>19</v>
+        <v>1653</v>
       </c>
       <c r="Q34" t="n">
-        <v>205</v>
+        <v>651</v>
       </c>
       <c r="R34" t="n">
-        <v>224</v>
+        <v>2304</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,12 +3724,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1498701834</t>
+          <t>35287626</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498701834</t>
+          <t>https://m.place.naver.com/place/35287626</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3658,34 +3746,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>온플릭휘트니스 백마역점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>onfleekfitness4@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1445-5805</t>
+          <t>0507-1389-9498</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기도 고양시 일산동구 경의로 315 지하1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3700,10 +3788,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y1xb</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3715,13 +3807,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>242</v>
+        <v>315</v>
       </c>
       <c r="Q35" t="n">
-        <v>441</v>
+        <v>121</v>
       </c>
       <c r="R35" t="n">
-        <v>683</v>
+        <v>436</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,12 +3822,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>1691525809</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/1691525809</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3752,29 +3844,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>인프라짐 PT 대화역헬스장</t>
+          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>infragym1@naver.com</t>
+          <t>kobygym@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1331-5665</t>
+          <t>0507-1374-2418</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/infragym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3784,23 +3876,27 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we6ins2</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3809,13 +3905,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2439</v>
+        <v>708</v>
       </c>
       <c r="Q36" t="n">
-        <v>2032</v>
+        <v>1005</v>
       </c>
       <c r="R36" t="n">
-        <v>4471</v>
+        <v>1713</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,12 +3920,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11579499</t>
+          <t>1332252606</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11579499</t>
+          <t>https://m.place.naver.com/place/1332252606</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3846,34 +3942,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>백석PT 짐플러스 휘트니스</t>
+          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>gymplus_fitness@naver.com</t>
+          <t>olof7l6h@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1370-0474</t>
+          <t>0507-1431-9036</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 지하1층 짐플러스휘트니스</t>
+          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymplus_fitness</t>
+          <t>https://link.inpock.co.kr/forestgym_2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3888,10 +3984,14 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yfab</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3903,13 +4003,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>80</v>
+        <v>852</v>
       </c>
       <c r="Q37" t="n">
-        <v>65</v>
+        <v>535</v>
       </c>
       <c r="R37" t="n">
-        <v>145</v>
+        <v>1387</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3918,12 +4018,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>38510579</t>
+          <t>1320621577</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38510579</t>
+          <t>https://m.place.naver.com/place/1320621577</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3940,29 +4040,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>스포애니 마두역점</t>
+          <t>크로스핏ATD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>spoany64@naver.com</t>
+          <t>bebetters@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1369-7697</t>
+          <t>0507-1352-5696</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
+          <t>경기도 고양시 일산서구 주화로 210 우리프라자 B1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany64</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3972,20 +4072,24 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ypr4</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -3997,13 +4101,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>488</v>
+        <v>15</v>
       </c>
       <c r="Q38" t="n">
-        <v>2210</v>
+        <v>46</v>
       </c>
       <c r="R38" t="n">
-        <v>2698</v>
+        <v>61</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4012,12 +4116,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1639489562</t>
+          <t>1758813134</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639489562</t>
+          <t>https://m.place.naver.com/place/1758813134</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4034,29 +4138,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5150피트니스 중산점</t>
+          <t>휘트니스바로 중산점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5150fitness5@naver.com</t>
+          <t>fitnessbaro@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1370-4847</t>
+          <t>0507-1467-5222</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 241 해태쇼핑타운 B1</t>
+          <t>경기도 고양시 일산동구 중산로 67 아카메디건물 5층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5150fitness5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4066,7 +4170,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4076,10 +4180,14 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42g1w</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>X</t>
@@ -4091,13 +4199,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>349</v>
+        <v>912</v>
       </c>
       <c r="Q39" t="n">
-        <v>406</v>
+        <v>254</v>
       </c>
       <c r="R39" t="n">
-        <v>755</v>
+        <v>1166</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4106,12 +4214,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2006347781</t>
+          <t>1120920642</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006347781</t>
+          <t>https://m.place.naver.com/place/1120920642</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4128,29 +4236,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>더스카이짐 본점</t>
+          <t>가온 휘트니스 대화마을점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>theskygym@naver.com</t>
+          <t>gaonfitness_@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1481-6336</t>
+          <t>031-919-6336</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 136 2층 더스카이짐</t>
+          <t>경기도 고양시 일산서구 송포로 35 2층 202호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theskygym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4160,20 +4268,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40pmy</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4185,13 +4297,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>306</v>
+        <v>980</v>
       </c>
       <c r="Q40" t="n">
-        <v>466</v>
+        <v>368</v>
       </c>
       <c r="R40" t="n">
-        <v>772</v>
+        <v>1348</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4200,12 +4312,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1360909658</t>
+          <t>1693727202</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1360909658</t>
+          <t>https://m.place.naver.com/place/1693727202</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4222,29 +4334,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>범휘트니스 일산점</t>
+          <t>메인 휘트니스 백마학원가점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>main_bacma@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1440-5101</t>
+          <t>0507-1489-2272</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일중로 17 포오스프라자 5층</t>
+          <t>경기도 고양시 일산동구 강촌로 157 서울코아 비층 비01호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4254,20 +4366,24 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46r15</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4279,13 +4395,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="Q41" t="n">
-        <v>396</v>
+        <v>157</v>
       </c>
       <c r="R41" t="n">
-        <v>598</v>
+        <v>342</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4294,12 +4410,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>31590084</t>
+          <t>1057482007</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31590084</t>
+          <t>https://m.place.naver.com/place/1057482007</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4316,29 +4432,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>핏포유 탄현점 헬스PT</t>
+          <t>범휘트니스 정발산점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>fit4u2019@naver.com</t>
+          <t>jibum903@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1363-6711</t>
+          <t>0507-1362-5111</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
+          <t>경기도 고양시 일산동구 일산로 432 5층 범휘트니스 정발산점</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fit4u2019</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4348,20 +4464,24 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whva77e</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>X</t>
@@ -4373,13 +4493,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>526</v>
+        <v>302</v>
       </c>
       <c r="Q42" t="n">
-        <v>5107</v>
+        <v>354</v>
       </c>
       <c r="R42" t="n">
-        <v>5633</v>
+        <v>656</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4388,12 +4508,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>60823193</t>
+          <t>1466459481</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60823193</t>
+          <t>https://m.place.naver.com/place/1466459481</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4410,29 +4530,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 일산점</t>
+          <t>범휘트니스 풍동점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rewind9089@naver.com</t>
+          <t>bumfitness6@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1414-2729</t>
+          <t>0507-1441-7530</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산동구 숲속마을1로 29-37 201호, 202호, 203호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://linktr.ee/junistar3579</t>
+          <t>https://blog.naver.com/bumfitness6/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4458,7 +4578,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4467,13 +4587,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="Q43" t="n">
-        <v>203</v>
+        <v>148</v>
       </c>
       <c r="R43" t="n">
-        <v>541</v>
+        <v>437</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4482,12 +4602,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1294694330</t>
+          <t>1604516167</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294694330</t>
+          <t>https://m.place.naver.com/place/1604516167</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4504,29 +4624,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>풍산휘트니스&amp;기구필라테스</t>
+          <t>스포애니 마두역점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>psfitness_pilates@naver.com</t>
+          <t>spoany64@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>031-976-6911</t>
+          <t>0507-1369-7697</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 하늘마을1로 2 풍산프라자 3층 전체</t>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/psfitness_pilates</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4536,20 +4656,24 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h0gc</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>X</t>
@@ -4561,13 +4685,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="Q44" t="n">
-        <v>559</v>
+        <v>2214</v>
       </c>
       <c r="R44" t="n">
-        <v>1034</v>
+        <v>2702</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4576,12 +4700,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>38425785</t>
+          <t>1639489562</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38425785</t>
+          <t>https://m.place.naver.com/place/1639489562</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4598,29 +4722,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>가온휘트니스 가좌 2호점</t>
+          <t>리스펙짐 PT 백석점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>gaonfitness2@naver.com</t>
+          <t>respect9696@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1358-8077</t>
+          <t>0507-1431-9696</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 송포로 261 101호 201호</t>
+          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gaonfitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4630,7 +4754,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4640,10 +4764,14 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7s4785</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4655,13 +4783,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="Q45" t="n">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="R45" t="n">
-        <v>340</v>
+        <v>496</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4670,12 +4798,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1261817011</t>
+          <t>1412423288</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261817011</t>
+          <t>https://m.place.naver.com/place/1412423288</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4692,29 +4820,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>더블에잇휘트니스 마두점</t>
+          <t>온플릭휘트니스 마두역점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>double7998@naver.com</t>
+          <t>onfleekfitness1@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1350-7998</t>
+          <t>0507-1367-9479</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1171 현대프리젠트 9,10층</t>
+          <t>경기도 고양시 일산동구 장백로 178 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://partner.talk.naver.com/web/accounts/101675659/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4724,7 +4852,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4734,13 +4862,17 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42jo1</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4749,13 +4881,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>287</v>
+        <v>509</v>
       </c>
       <c r="Q46" t="n">
-        <v>735</v>
+        <v>190</v>
       </c>
       <c r="R46" t="n">
-        <v>1022</v>
+        <v>699</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4764,12 +4896,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1951351429</t>
+          <t>1196366994</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951351429</t>
+          <t>https://m.place.naver.com/place/1196366994</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4786,30 +4918,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>범휘트니스 마두점</t>
+          <t>짐박스피트니스 탄현제니스점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bummadu@naver.com</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1458-0638</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 328 지하층 101, 102, 103호</t>
+          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bumfitness.madu/</t>
+          <t>https://gymboxx.com/onceinayear?gym=80</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4819,18 +4959,22 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4839,13 +4983,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>383</v>
+        <v>754</v>
       </c>
       <c r="Q47" t="n">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="R47" t="n">
-        <v>491</v>
+        <v>787</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4854,12 +4998,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1200977920</t>
+          <t>2038926940</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200977920</t>
+          <t>https://m.place.naver.com/place/2038926940</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4876,29 +5020,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>더스카이짐 정발산점</t>
+          <t>바디에이원짐 헬스/PT/재활</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>theskygym2@naver.com</t>
+          <t>art729@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1491-4450</t>
+          <t>0507-1406-1457</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 428 5층 더스카이짐 정발산점</t>
+          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theskygym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4908,20 +5052,24 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5x0ez</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>X</t>
@@ -4933,13 +5081,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>68</v>
+        <v>543</v>
       </c>
       <c r="Q48" t="n">
-        <v>179</v>
+        <v>335</v>
       </c>
       <c r="R48" t="n">
-        <v>247</v>
+        <v>878</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4948,12 +5096,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1311260923</t>
+          <t>1241623010</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311260923</t>
+          <t>https://m.place.naver.com/place/1241623010</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4970,29 +5118,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5002,20 +5150,24 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu9oxes</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>X</t>
@@ -5027,13 +5179,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>615</v>
+        <v>243</v>
       </c>
       <c r="Q49" t="n">
-        <v>792</v>
+        <v>441</v>
       </c>
       <c r="R49" t="n">
-        <v>1407</v>
+        <v>684</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5042,12 +5194,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5064,29 +5216,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>메인 휘트니스 후곡점</t>
+          <t>리스펙짐 PT 마두점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>main2211@naver.com</t>
+          <t>respect1333@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1484-2212</t>
+          <t>0507-1335-1380</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 529 대화프라자 B동 지하1층 메인 휘트니스</t>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/main2211</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5096,20 +5248,24 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lzon</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>X</t>
@@ -5121,13 +5277,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>200</v>
+        <v>1376</v>
       </c>
       <c r="Q50" t="n">
-        <v>286</v>
+        <v>1392</v>
       </c>
       <c r="R50" t="n">
-        <v>486</v>
+        <v>2768</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5136,12 +5292,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1308136724</t>
+          <t>1420492815</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1308136724</t>
+          <t>https://m.place.naver.com/place/1420492815</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5158,29 +5314,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>툭짐</t>
+          <t>MTO 피트니스 PT 정발산점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ksm19088@naver.com</t>
+          <t>jbsfitness@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1313-1590</t>
+          <t>0507-1467-8389</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1195 지1층 비101호</t>
+          <t>경기도 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/took.gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5190,7 +5346,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5200,10 +5356,14 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f6xw</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>X</t>
@@ -5215,13 +5375,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>728</v>
       </c>
       <c r="R51" t="n">
-        <v>213</v>
+        <v>1157</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5230,12 +5390,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2042000567</t>
+          <t>1314564243</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042000567</t>
+          <t>https://m.place.naver.com/place/1314564243</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5252,52 +5412,56 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>온플릭휘트니스 대화점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>onfleek_fitness@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1382-6682</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기도 고양시 일산서구 중앙로 1573 킨텍스프라자 9층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42cu2</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>O</t>
@@ -5309,13 +5473,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1187</v>
+        <v>325</v>
       </c>
       <c r="Q52" t="n">
-        <v>803</v>
+        <v>326</v>
       </c>
       <c r="R52" t="n">
-        <v>1990</v>
+        <v>651</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5324,12 +5488,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1050985755</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1050985755</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5346,29 +5510,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>원잇핏 PT&amp;헬스</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>oneitfit@naver.com</t>
+          <t>resort_13@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1400-8861</t>
+          <t>0507-1434-4080</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oneitfit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5378,23 +5542,27 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zymk</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5403,13 +5571,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>229</v>
+        <v>561</v>
       </c>
       <c r="Q53" t="n">
-        <v>594</v>
+        <v>900</v>
       </c>
       <c r="R53" t="n">
-        <v>823</v>
+        <v>1461</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5418,12 +5586,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13223584</t>
+          <t>1379874016</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13223584</t>
+          <t>https://m.place.naver.com/place/1379874016</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5440,29 +5608,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>크로스핏 GK 일산 마두점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>la40012@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1310-9524</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산동구 강석로 113 지하1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://cafe.naver.com/cfgkmd</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5497,13 +5665,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1221</v>
+        <v>266</v>
       </c>
       <c r="Q54" t="n">
-        <v>1612</v>
+        <v>412</v>
       </c>
       <c r="R54" t="n">
-        <v>2833</v>
+        <v>678</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5512,12 +5680,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1085090977</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1085090977</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5534,34 +5702,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
+          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>maxoutfitness_3@naver.com</t>
+          <t>kann5555@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1378-6366</t>
+          <t>0507-1396-3191</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maxoutfitness__2/</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5571,18 +5739,22 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41bm5</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5591,13 +5763,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1272</v>
+        <v>2042</v>
       </c>
       <c r="Q55" t="n">
-        <v>203</v>
+        <v>928</v>
       </c>
       <c r="R55" t="n">
-        <v>1475</v>
+        <v>2970</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5606,12 +5778,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1674766909</t>
+          <t>1797149054</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674766909</t>
+          <t>https://m.place.naver.com/place/1797149054</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5628,34 +5800,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>바디에이원짐 헬스/PT/재활</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>art729@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1406-1457</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/art729/224075467295</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5670,28 +5842,32 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4skng</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>542</v>
+        <v>1187</v>
       </c>
       <c r="Q56" t="n">
-        <v>335</v>
+        <v>803</v>
       </c>
       <c r="R56" t="n">
-        <v>877</v>
+        <v>1990</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5700,12 +5876,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1241623010</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241623010</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5717,34 +5893,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+          <t>온플릭휘트니스 일산역점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>lifetime1231@naver.com</t>
+          <t>onfleek555@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1355-9897</t>
+          <t>0507-1319-9498</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+          <t>경기도 고양시 일산서구 경의로 665 501호, 502호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lifetime1231/223007274910</t>
+          <t>https://blog.naver.com/onfleek555</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5779,13 +5955,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>491</v>
+        <v>157</v>
       </c>
       <c r="Q57" t="n">
-        <v>1140</v>
+        <v>140</v>
       </c>
       <c r="R57" t="n">
-        <v>1631</v>
+        <v>297</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5794,12 +5970,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1618140538</t>
+          <t>1112352231</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618140538</t>
+          <t>https://m.place.naver.com/place/1112352231</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5816,29 +5992,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>범휘트니스 정발산점</t>
+          <t>범휘트니스 마두점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jibum903@naver.com</t>
+          <t>bummadu@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1362-5111</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 432 5층 범휘트니스 정발산점</t>
+          <t>경기도 고양시 일산동구 일산로 328 지하층 101, 102, 103호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jibum903</t>
+          <t>https://www.instagram.com/bumfitness.madu/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5853,7 +6025,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5873,13 +6045,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="Q58" t="n">
-        <v>354</v>
+        <v>108</v>
       </c>
       <c r="R58" t="n">
-        <v>656</v>
+        <v>491</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5888,12 +6060,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1466459481</t>
+          <t>1200977920</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466459481</t>
+          <t>https://m.place.naver.com/place/1200977920</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5910,29 +6082,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>온플릭휘트니스 백마역점</t>
+          <t>리와인드 휘트니스 중산점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>onfleekfitness4@naver.com</t>
+          <t>rewind_8990@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1389-9498</t>
+          <t>0507-1300-9146</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 경의로 315 지하1층</t>
+          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onfleekfitness4/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5942,7 +6114,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5952,10 +6124,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u1uf</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>X</t>
@@ -5967,13 +6143,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>316</v>
+        <v>167</v>
       </c>
       <c r="Q59" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="R59" t="n">
-        <v>437</v>
+        <v>305</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5982,12 +6158,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1691525809</t>
+          <t>1726802714</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691525809</t>
+          <t>https://m.place.naver.com/place/1726802714</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6004,29 +6180,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>온플릭휘트니스 대화점</t>
+          <t>F45 일산</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>onfleek_fitness@naver.com</t>
+          <t>f45_ilsan@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1382-6682</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1573 킨텍스프라자 9층</t>
+          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 2층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onfleek_fitness_/?igshid=MmIzYWVlNDQ5Yg%3D%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6036,7 +6208,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6052,7 +6224,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6061,13 +6233,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>325</v>
+        <v>119</v>
       </c>
       <c r="Q60" t="n">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="R60" t="n">
-        <v>651</v>
+        <v>350</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6076,12 +6248,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1050985755</t>
+          <t>1034749202</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050985755</t>
+          <t>https://m.place.naver.com/place/1034749202</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6098,44 +6270,44 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
+          <t>휘트니스피플 우먼 탄현점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>woduddl01@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1431-9036</t>
+          <t>0507-1321-3912</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
+          <t>경기도 고양시 일산서구 일현로 65 동현빌딩 3층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/forestgym_2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6145,7 +6317,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yfab</t>
+          <t>https://talk.naver.com/ct/wbpmpn7</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6159,13 +6331,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>852</v>
+        <v>903</v>
       </c>
       <c r="Q61" t="n">
-        <v>535</v>
+        <v>1217</v>
       </c>
       <c r="R61" t="n">
-        <v>1387</v>
+        <v>2120</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6174,12 +6346,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1320621577</t>
+          <t>1845503473</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320621577</t>
+          <t>https://m.place.naver.com/place/1845503473</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6196,25 +6368,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>F45 일산</t>
+          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>f45_ilsan@naver.com</t>
+          <t>maxoutfitness_1@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1378-6366</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 2층</t>
+          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f45_ilsan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6224,20 +6400,24 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42bdj</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6249,13 +6429,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>119</v>
+        <v>1273</v>
       </c>
       <c r="Q62" t="n">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="R62" t="n">
-        <v>349</v>
+        <v>1476</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6264,12 +6444,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1034749202</t>
+          <t>1674766909</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034749202</t>
+          <t>https://m.place.naver.com/place/1674766909</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6286,29 +6466,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>리스펙짐 PT 백석점</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>respect9696@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1431-9696</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/respectgym3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6318,7 +6498,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6328,10 +6508,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461vb</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6343,13 +6527,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>210</v>
+        <v>679</v>
       </c>
       <c r="Q63" t="n">
-        <v>286</v>
+        <v>1053</v>
       </c>
       <c r="R63" t="n">
-        <v>496</v>
+        <v>1732</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6358,12 +6542,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1412423288</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1412423288</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6380,29 +6564,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 탄현점</t>
+          <t>리와인드 휘트니스 일산점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>rewind9089@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1321-3912</t>
+          <t>0507-1414-2729</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 65 동현빌딩 3층</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://linktr.ee/junistar3579</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6422,13 +6606,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45mlf</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6437,13 +6625,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>903</v>
+        <v>338</v>
       </c>
       <c r="Q64" t="n">
-        <v>1217</v>
+        <v>203</v>
       </c>
       <c r="R64" t="n">
-        <v>2120</v>
+        <v>541</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6452,12 +6640,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1845503473</t>
+          <t>1294694330</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845503473</t>
+          <t>https://m.place.naver.com/place/1294694330</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6474,29 +6662,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>범휘트니스 풍동점</t>
+          <t>제이앤제이 피트니스 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bumfitness6@naver.com</t>
+          <t>likegym_@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1441-7530</t>
+          <t>0507-1314-9695</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을1로 29-37 201호, 202호, 203호</t>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 2층 제이앤제이 피트니스</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bumfitness6/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6506,20 +6694,24 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rtjn</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>X</t>
@@ -6531,13 +6723,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>289</v>
+        <v>450</v>
       </c>
       <c r="Q65" t="n">
-        <v>148</v>
+        <v>303</v>
       </c>
       <c r="R65" t="n">
-        <v>437</v>
+        <v>753</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6546,12 +6738,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1604516167</t>
+          <t>1181142706</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604516167</t>
+          <t>https://m.place.naver.com/place/1181142706</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6568,29 +6760,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>메인 휘트니스 백마학원가점</t>
+          <t>더스카이짐 정발산점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>main_bacma@naver.com</t>
+          <t>theskygym2@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1489-2272</t>
+          <t>0507-1491-4450</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강촌로 157 서울코아 비층 비01호</t>
+          <t>경기도 고양시 일산동구 일산로 428 5층 더스카이짐 정발산점</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/main_bacma</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6600,20 +6792,24 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ia7o</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>X</t>
@@ -6621,17 +6817,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="Q66" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="R66" t="n">
-        <v>342</v>
+        <v>247</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6640,12 +6836,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1057482007</t>
+          <t>1311260923</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057482007</t>
+          <t>https://m.place.naver.com/place/1311260923</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6662,52 +6858,56 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>제이앤제이 피트니스 헬스&amp;PT&amp;필라테스</t>
+          <t>짐300</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>likegym_@naver.com</t>
+          <t>gym_300@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1314-9695</t>
+          <t>0507-1376-6714</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 181 일산프라자 2층 제이앤제이 피트니스</t>
+          <t>경기도 고양시 일산서구 고양대로 666 지하1층 M111, 112, 114, 115호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jnjfitness_madu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/weq3d0n</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6719,13 +6919,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="Q67" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="R67" t="n">
-        <v>753</v>
+        <v>610</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6734,12 +6934,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1181142706</t>
+          <t>1408702037</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181142706</t>
+          <t>https://m.place.naver.com/place/1408702037</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6751,34 +6951,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>헬로우짐 헬스&amp;PT 백석점</t>
+          <t>범휘트니스 일산점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>hellogym001@naver.com</t>
+          <t>bum903@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1383-8244</t>
+          <t>0507-1440-5101</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
+          <t>경기도 고양시 일산서구 일중로 17 포오스프라자 5층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellogym001</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6788,20 +6988,24 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc5xkd</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6813,13 +7017,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="Q68" t="n">
-        <v>220</v>
+        <v>396</v>
       </c>
       <c r="R68" t="n">
-        <v>320</v>
+        <v>598</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6828,12 +7032,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1528105437</t>
+          <t>31590084</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528105437</t>
+          <t>https://m.place.naver.com/place/31590084</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6850,29 +7054,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>프라임핏 헬스&amp;PT 식사점</t>
+          <t>베르만짐 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>primefit_fitness@naver.com</t>
+          <t>qpfmaks02@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>031-962-2306</t>
+          <t>0507-1349-2708</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
+          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/prime_fit1/?igshid=MWpldjY4Y3h2dDF4ag%3D%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6882,7 +7086,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6892,13 +7096,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjxd4y3</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6907,13 +7115,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1127</v>
+        <v>323</v>
       </c>
       <c r="Q69" t="n">
-        <v>289</v>
+        <v>669</v>
       </c>
       <c r="R69" t="n">
-        <v>1416</v>
+        <v>992</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6922,12 +7130,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1328418362</t>
+          <t>1722963960</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328418362</t>
+          <t>https://m.place.naver.com/place/1722963960</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6944,29 +7152,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>플렉스짐</t>
+          <t>프라임핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>flexgymilsan@naver.com</t>
+          <t>primefit_fitness@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1401-3798</t>
+          <t>031-962-2306</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고봉로 32-19 남정씨티프라자7차 2층</t>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flexgym_ilsan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6976,7 +7184,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7001,13 +7209,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>323</v>
+        <v>1127</v>
       </c>
       <c r="Q70" t="n">
-        <v>868</v>
+        <v>289</v>
       </c>
       <c r="R70" t="n">
-        <v>1191</v>
+        <v>1416</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7016,12 +7224,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>36615589</t>
+          <t>1328418362</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615589</t>
+          <t>https://m.place.naver.com/place/1328418362</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7038,29 +7246,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>더핏퍼스널트레이닝</t>
+          <t>헌드레드짐 파주운정점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sky_se@naver.com</t>
+          <t>hundredgym@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1411-0772</t>
+          <t>0507-1327-5413</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sky_se/223038038455</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7070,12 +7278,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7095,13 +7303,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>181</v>
+        <v>528</v>
       </c>
       <c r="Q71" t="n">
-        <v>1127</v>
+        <v>203</v>
       </c>
       <c r="R71" t="n">
-        <v>1308</v>
+        <v>731</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7110,12 +7318,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1707178271</t>
+          <t>1101743632</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707178271</t>
+          <t>https://m.place.naver.com/place/1101743632</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7132,29 +7340,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>더핏퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>sky_se@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1381-8260</t>
+          <t>0507-1411-0772</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7164,20 +7372,24 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4izrx</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>X</t>
@@ -7189,13 +7401,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="Q72" t="n">
-        <v>510</v>
+        <v>1127</v>
       </c>
       <c r="R72" t="n">
-        <v>643</v>
+        <v>1308</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7204,12 +7416,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>32507674</t>
+          <t>1707178271</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32507674</t>
+          <t>https://m.place.naver.com/place/1707178271</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7226,29 +7438,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>헌드레드짐 파주운정점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>hundredgym@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1327-5413</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/donghyeok_hundredgym/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7258,7 +7470,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7268,10 +7480,14 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
@@ -7283,13 +7499,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>528</v>
+        <v>1353</v>
       </c>
       <c r="Q73" t="n">
-        <v>203</v>
+        <v>341</v>
       </c>
       <c r="R73" t="n">
-        <v>731</v>
+        <v>1694</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7298,12 +7514,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1101743632</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101743632</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7320,29 +7536,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7352,20 +7568,24 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7377,13 +7597,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1353</v>
+        <v>1251</v>
       </c>
       <c r="Q74" t="n">
-        <v>341</v>
+        <v>1089</v>
       </c>
       <c r="R74" t="n">
-        <v>1694</v>
+        <v>2340</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7392,12 +7612,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7414,29 +7634,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>저스트플레잉</t>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>justplaying@naver.com</t>
+          <t>bodyoffgym@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>031-965-1106</t>
+          <t>0507-1381-8260</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://justplaying.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7446,7 +7666,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7467,17 +7687,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="Q75" t="n">
-        <v>407</v>
+        <v>510</v>
       </c>
       <c r="R75" t="n">
-        <v>534</v>
+        <v>643</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7486,12 +7706,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>37452748</t>
+          <t>32507674</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37452748</t>
+          <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7508,29 +7728,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>저스트플레잉</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>justplaying@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>031-965-1106</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>http://justplaying.co.kr/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7561,17 +7781,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1250</v>
+        <v>127</v>
       </c>
       <c r="Q76" t="n">
-        <v>1089</v>
+        <v>407</v>
       </c>
       <c r="R76" t="n">
-        <v>2339</v>
+        <v>534</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7580,12 +7800,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>37452748</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/37452748</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 일산점</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rewind9089@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1414-2729</t>
+          <t>0507-1373-7656</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://linktr.ee/junistar3579</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>338</v>
+        <v>617</v>
       </c>
       <c r="Q2" t="n">
-        <v>203</v>
+        <v>792</v>
       </c>
       <c r="R2" t="n">
-        <v>541</v>
+        <v>1409</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1294694330</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294694330</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 중산점</t>
+          <t>리와인드 휘트니스 일산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rewind_8990@naver.com</t>
+          <t>rewind9089@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1300-9146</t>
+          <t>0507-1414-2729</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rewind_fitness2</t>
+          <t>https://linktr.ee/junistar3579</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>167</v>
+        <v>338</v>
       </c>
       <c r="Q3" t="n">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="R3" t="n">
-        <v>305</v>
+        <v>541</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1726802714</t>
+          <t>1294694330</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726802714</t>
+          <t>https://m.place.naver.com/place/1294694330</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -846,34 +846,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>짐박스피트니스 탄현제니스점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>0507-1458-0638</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://gymboxx.com/onceinayear?gym=80</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>617</v>
+        <v>754</v>
       </c>
       <c r="Q5" t="n">
-        <v>792</v>
+        <v>33</v>
       </c>
       <c r="R5" t="n">
-        <v>1409</v>
+        <v>787</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>2038926940</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/2038926940</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,38 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐박스피트니스 탄현제니스점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1458-0638</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>754</v>
+        <v>1221</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>1612</v>
       </c>
       <c r="R6" t="n">
-        <v>787</v>
+        <v>2833</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2038926940</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,34 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1221</v>
+        <v>1187</v>
       </c>
       <c r="Q7" t="n">
-        <v>1612</v>
+        <v>803</v>
       </c>
       <c r="R7" t="n">
-        <v>2833</v>
+        <v>1990</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1187</v>
+        <v>243</v>
       </c>
       <c r="Q8" t="n">
-        <v>803</v>
+        <v>441</v>
       </c>
       <c r="R8" t="n">
-        <v>1990</v>
+        <v>684</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-943-0116</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hgym24/</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>367</v>
+        <v>678</v>
       </c>
       <c r="Q9" t="n">
-        <v>420</v>
+        <v>1055</v>
       </c>
       <c r="R9" t="n">
-        <v>787</v>
+        <v>1733</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>548127191</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548127191</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,34 +1320,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>머스타드피트니스 운정점</t>
+          <t>에이치짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mustard_fitness3@naver.com</t>
+          <t>ssj783312@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1403-6882</t>
+          <t>031-943-0116</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
+          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.mustard-fitness.com</t>
+          <t>https://www.instagram.com/hgym24/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1042</v>
+        <v>367</v>
       </c>
       <c r="Q10" t="n">
-        <v>124</v>
+        <v>420</v>
       </c>
       <c r="R10" t="n">
-        <v>1166</v>
+        <v>787</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>584588992</t>
+          <t>548127191</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/584588992</t>
+          <t>https://m.place.naver.com/place/548127191</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1474,10 +1474,10 @@
         <v>304</v>
       </c>
       <c r="Q11" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R11" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1503,34 +1503,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>다다짐 헬스&amp;PT 운정본점</t>
+          <t>에이플러스짐 PT 중산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dadagym@naver.com</t>
+          <t>aplusgym600@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1304-1646</t>
+          <t>031-977-5755</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 파주시 미래로602번길 11 701호,702호</t>
+          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dadagym/224242550028</t>
+          <t>https://blog.naver.com/aplusgym600/222983159417</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1550,14 +1550,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4v2ogs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1569,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>59</v>
+        <v>490</v>
       </c>
       <c r="Q12" t="n">
-        <v>70</v>
+        <v>740</v>
       </c>
       <c r="R12" t="n">
-        <v>129</v>
+        <v>1230</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,109 +1580,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1236035000</t>
+          <t>1426431657</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236035000</t>
+          <t>https://m.place.naver.com/place/1426431657</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>투게더휘트니스 일산점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>togetherfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1461-1485</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/togetherfitness</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1353</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>341</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1694</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1161506645</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dgq8</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -624,10 +628,10 @@
         <v>617</v>
       </c>
       <c r="Q2" t="n">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R2" t="n">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45mlf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -718,10 +726,10 @@
         <v>338</v>
       </c>
       <c r="Q3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R3" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,12 +777,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/infragym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +792,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9v3</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -846,38 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐박스피트니스 탄현제니스점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1458-0638</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -892,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>754</v>
+        <v>1221</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>1612</v>
       </c>
       <c r="R5" t="n">
-        <v>787</v>
+        <v>2833</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2038926940</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,34 +956,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>짐박스피트니스 탄현제니스점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1458-0638</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://gymboxx.com/onceinayear?gym=80</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -986,13 +1002,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1221</v>
+        <v>754</v>
       </c>
       <c r="Q6" t="n">
-        <v>1612</v>
+        <v>33</v>
       </c>
       <c r="R6" t="n">
-        <v>2833</v>
+        <v>787</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1036,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>2038926940</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/2038926940</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,34 +1058,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>식스틴 휘트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>sixteen_fitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1428-1174</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기 고양시 일산동구 성석로 7 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,18 +1091,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40gss</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1187</v>
+        <v>177</v>
       </c>
       <c r="Q7" t="n">
-        <v>803</v>
+        <v>464</v>
       </c>
       <c r="R7" t="n">
-        <v>1990</v>
+        <v>641</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1004973811</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1004973811</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,52 +1152,56 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1445-5805</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461vb</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>243</v>
+        <v>678</v>
       </c>
       <c r="Q8" t="n">
-        <v>441</v>
+        <v>1056</v>
       </c>
       <c r="R8" t="n">
-        <v>684</v>
+        <v>1734</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>에이치짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>ssj783312@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>031-943-0116</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/readybody2</t>
+          <t>https://www.instagram.com/hgym24/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>678</v>
+        <v>367</v>
       </c>
       <c r="Q9" t="n">
-        <v>1055</v>
+        <v>420</v>
       </c>
       <c r="R9" t="n">
-        <v>1733</v>
+        <v>787</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>548127191</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/548127191</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,34 +1344,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>머스타드피트니스 운정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>mustard_fitness3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-943-0116</t>
+          <t>0507-1403-6882</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hgym24/</t>
+          <t>http://www.mustard-fitness.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1357,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>367</v>
+        <v>1042</v>
       </c>
       <c r="Q10" t="n">
-        <v>420</v>
+        <v>124</v>
       </c>
       <c r="R10" t="n">
-        <v>787</v>
+        <v>1166</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>548127191</t>
+          <t>584588992</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548127191</t>
+          <t>https://m.place.naver.com/place/584588992</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>프라임핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>primefit_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>031-962-2306</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
+          <t>https://www.instagram.com/prime_fit1/?igshid=MWpldjY4Y3h2dDF4ag%3D%3D</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>304</v>
+        <v>1127</v>
       </c>
       <c r="Q11" t="n">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="R11" t="n">
-        <v>573</v>
+        <v>1416</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>1328418362</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/1328418362</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1525,12 +1549,12 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym600/222983159417</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1540,20 +1564,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2t1k29</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1565,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q12" t="n">
         <v>740</v>
       </c>
       <c r="R12" t="n">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>리와인드 휘트니스 일산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
+          <t>rewind9089@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>0507-1414-2729</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://linktr.ee/junistar3579</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dgq8</t>
+          <t>https://talk.naver.com/ct/w45mlf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>617</v>
+        <v>338</v>
       </c>
       <c r="Q2" t="n">
-        <v>791</v>
+        <v>204</v>
       </c>
       <c r="R2" t="n">
-        <v>1408</v>
+        <v>542</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>1294694330</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/1294694330</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 일산점</t>
+          <t>리와인드 휘트니스 중산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rewind9089@naver.com</t>
+          <t>rewind_8990@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1414-2729</t>
+          <t>0507-1300-9146</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://linktr.ee/junistar3579</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45mlf</t>
+          <t>https://talk.naver.com/ct/w5u1uf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="Q3" t="n">
-        <v>204</v>
+        <v>138</v>
       </c>
       <c r="R3" t="n">
-        <v>542</v>
+        <v>305</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1294694330</t>
+          <t>1726802714</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294694330</t>
+          <t>https://m.place.naver.com/place/1726802714</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2439</v>
+        <v>2443</v>
       </c>
       <c r="Q4" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="R4" t="n">
-        <v>4471</v>
+        <v>4476</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1373-7656</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
+          <t>https://talk.naver.com/ct/w4dgq8</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1221</v>
+        <v>617</v>
       </c>
       <c r="Q5" t="n">
-        <v>1612</v>
+        <v>791</v>
       </c>
       <c r="R5" t="n">
-        <v>2833</v>
+        <v>1408</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -956,48 +956,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐박스피트니스 탄현제니스점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1458-0638</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1007,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>754</v>
+        <v>1222</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>1612</v>
       </c>
       <c r="R6" t="n">
-        <v>787</v>
+        <v>2834</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2038926940</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1058,30 +1054,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>식스틴 휘트니스</t>
+          <t>짐박스피트니스 탄현제니스점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sixteen_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1458-0638</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 성석로 7 2층</t>
+          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
+          <t>https://gymboxx.com/onceinayear?gym=80</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1105,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40gss</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>177</v>
+        <v>755</v>
       </c>
       <c r="Q7" t="n">
-        <v>464</v>
+        <v>33</v>
       </c>
       <c r="R7" t="n">
-        <v>641</v>
+        <v>788</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1134,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1004973811</t>
+          <t>2038926940</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004973811</t>
+          <t>https://m.place.naver.com/place/2038926940</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1156,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>식스틴 휘트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>sixteen_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1359-9680</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 고양시 일산동구 성석로 7 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/readybody2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w461vb</t>
+          <t>https://talk.naver.com/ct/w40gss</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>678</v>
+        <v>177</v>
       </c>
       <c r="Q8" t="n">
-        <v>1056</v>
+        <v>464</v>
       </c>
       <c r="R8" t="n">
-        <v>1734</v>
+        <v>641</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>1004973811</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/1004973811</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hgym24/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1298,7 +1298,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1310,10 +1310,10 @@
         <v>367</v>
       </c>
       <c r="Q9" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="R9" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1344,52 +1344,56 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>머스타드피트니스 운정점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mustard_fitness3@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1403-6882</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.mustard-fitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42s1j</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1042</v>
+        <v>304</v>
       </c>
       <c r="Q10" t="n">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="R10" t="n">
-        <v>1166</v>
+        <v>573</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>584588992</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/584588992</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1442,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>프라임핏 헬스&amp;PT 식사점</t>
+          <t>에이펙스 화정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>primefit_fitness@naver.com</t>
+          <t>kimeunmi_o@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>031-962-2306</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
+          <t>경기도 고양시 덕양구 화신로 263 브릿지타워 10층 전체호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/prime_fit1/?igshid=MWpldjY4Y3h2dDF4ag%3D%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1480,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ezo9</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1127</v>
+        <v>640</v>
       </c>
       <c r="Q11" t="n">
-        <v>289</v>
+        <v>507</v>
       </c>
       <c r="R11" t="n">
-        <v>1416</v>
+        <v>1147</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,115 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1328418362</t>
+          <t>1298459844</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328418362</t>
+          <t>https://m.place.naver.com/place/1298459844</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>에이플러스짐 PT 중산점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>aplusgym600@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>031-977-5755</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w2t1k29</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>489</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>740</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1229</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1426431657</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1426431657</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q2" t="n">
         <v>204</v>
       </c>
       <c r="R2" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,44 +662,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 중산점</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rewind_8990@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1300-9146</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u1uf</t>
+          <t>https://talk.naver.com/ct/w4skng</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>167</v>
+        <v>1186</v>
       </c>
       <c r="Q3" t="n">
-        <v>138</v>
+        <v>799</v>
       </c>
       <c r="R3" t="n">
-        <v>305</v>
+        <v>1985</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1726802714</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726802714</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인프라짐 PT 대화역헬스장</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>infragym1@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1331-5665</t>
+          <t>0507-1373-7656</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u9v3</t>
+          <t>https://talk.naver.com/ct/w4dgq8</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2443</v>
+        <v>617</v>
       </c>
       <c r="Q4" t="n">
-        <v>2033</v>
+        <v>791</v>
       </c>
       <c r="R4" t="n">
-        <v>4476</v>
+        <v>1408</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>11579499</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11579499</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,34 +858,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>짐박스피트니스 탄현제니스점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>0507-1458-0638</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://gymboxx.com/onceinayear?gym=80</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dgq8</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>617</v>
+        <v>755</v>
       </c>
       <c r="Q5" t="n">
-        <v>791</v>
+        <v>33</v>
       </c>
       <c r="R5" t="n">
-        <v>1408</v>
+        <v>788</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +938,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>2038926940</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/2038926940</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +960,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>식스틴 휘트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>sixteen_fitness@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1348-8027</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기 고양시 일산동구 성석로 7 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
+          <t>https://talk.naver.com/ct/w40gss</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1222</v>
+        <v>177</v>
       </c>
       <c r="Q6" t="n">
-        <v>1612</v>
+        <v>468</v>
       </c>
       <c r="R6" t="n">
-        <v>2834</v>
+        <v>645</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1004973811</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1004973811</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,38 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐박스피트니스 탄현제니스점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1458-0638</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1105,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1119,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>755</v>
+        <v>1224</v>
       </c>
       <c r="Q7" t="n">
-        <v>33</v>
+        <v>1611</v>
       </c>
       <c r="R7" t="n">
-        <v>788</v>
+        <v>2835</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2038926940</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1156,25 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>식스틴 휘트니스</t>
+          <t>세븐짐 탄현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sixteen_fitness@naver.com</t>
+          <t>sevengym_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1488-5258</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 성석로 7 2층</t>
+          <t>경기 고양시 일산서구 산현로17번길 9 부건3차프라자 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sevengym2008?igsh=amV0bGd5dWFnejNx</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40gss</t>
+          <t>https://talk.naver.com/ct/w5uzxl</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>464</v>
+        <v>152</v>
       </c>
       <c r="R8" t="n">
-        <v>641</v>
+        <v>319</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1004973811</t>
+          <t>12753889</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004973811</t>
+          <t>https://m.place.naver.com/place/12753889</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>에이펙스 화정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>kimeunmi_o@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>031-943-0116</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기 고양시 덕양구 화신로 263 브릿지타워 10층 전체호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/apex_gym_01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,13 +1288,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ezo9</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>367</v>
+        <v>641</v>
       </c>
       <c r="Q9" t="n">
-        <v>421</v>
+        <v>507</v>
       </c>
       <c r="R9" t="n">
-        <v>788</v>
+        <v>1148</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>548127191</t>
+          <t>1298459844</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548127191</t>
+          <t>https://m.place.naver.com/place/1298459844</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>에이플러스짐 PT 중산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>aplusgym600@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>031-977-5755</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/aplusgym600/222983159417</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42s1j</t>
+          <t>https://talk.naver.com/ct/w2t1k29</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>304</v>
+        <v>489</v>
       </c>
       <c r="Q10" t="n">
-        <v>269</v>
+        <v>740</v>
       </c>
       <c r="R10" t="n">
-        <v>573</v>
+        <v>1229</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>1426431657</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/1426431657</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,30 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이펙스 화정점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kimeunmi_o@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1461-1485</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 화신로 263 브릿지타워 10층 전체호</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,12 +1474,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ezo9</t>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>640</v>
+        <v>1356</v>
       </c>
       <c r="Q11" t="n">
-        <v>507</v>
+        <v>350</v>
       </c>
       <c r="R11" t="n">
-        <v>1147</v>
+        <v>1706</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1298459844</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1298459844</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/일산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/일산_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45mlf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q2" t="n">
         <v>204</v>
       </c>
       <c r="R2" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>바디에이원짐 헬스/PT/재활</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>art729@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1406-1457</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://blog.naver.com/art729/224075467295</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -704,32 +700,28 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4skng</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1186</v>
+        <v>544</v>
       </c>
       <c r="Q3" t="n">
-        <v>799</v>
+        <v>335</v>
       </c>
       <c r="R3" t="n">
-        <v>1985</v>
+        <v>879</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1241623010</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1241623010</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>더스카이짐 본점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
+          <t>theskygym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>0507-1481-6336</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기도 고양시 일산서구 원일로 136 2층 더스카이짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://blog.naver.com/theskygym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dgq8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>617</v>
+        <v>307</v>
       </c>
       <c r="Q4" t="n">
-        <v>791</v>
+        <v>468</v>
       </c>
       <c r="R4" t="n">
-        <v>1408</v>
+        <v>775</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,60 +824,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>1360909658</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/1360909658</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐박스피트니스 탄현제니스점</t>
+          <t>고포잇짐 헬스&amp;PT 장항점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>go4itgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1458-0638</t>
+          <t>0507-1315-5550</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
+          <t>https://blog.naver.com/go4itgym1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -904,17 +888,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -923,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>755</v>
+        <v>164</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>711</v>
       </c>
       <c r="R5" t="n">
-        <v>788</v>
+        <v>875</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,47 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2038926940</t>
+          <t>1738952122</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
+          <t>https://m.place.naver.com/place/1738952122</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>식스틴 휘트니스</t>
+          <t>에이치핏PT&amp;헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sixteen_fitness@naver.com</t>
+          <t>dngus8888@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1426-3482</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 성석로 7 2층</t>
+          <t>경기도 고양시 일산서구 중앙로 1547 3층 307호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
+          <t>https://blog.naver.com/dngus8888</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,19 +977,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40gss</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="n">
-        <v>468</v>
+        <v>336</v>
       </c>
       <c r="R6" t="n">
-        <v>645</v>
+        <v>408</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1004973811</t>
+          <t>1639222494</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004973811</t>
+          <t>https://m.place.naver.com/place/1639222494</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>1986피트니스 헬스PT 24시 중산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>1986fitness3@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1348-8027</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산동구 중산로 244 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://blog.naver.com/1986fitness3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1224</v>
+        <v>1306</v>
       </c>
       <c r="Q7" t="n">
-        <v>1611</v>
+        <v>1297</v>
       </c>
       <c r="R7" t="n">
-        <v>2835</v>
+        <v>2603</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1052772360</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1052772360</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>세븐짐 탄현점</t>
+          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sevengym_@naver.com</t>
+          <t>gymcare24@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1488-5258</t>
+          <t>0507-1483-3436</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 산현로17번길 9 부건3차프라자 6층</t>
+          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sevengym2008?igsh=amV0bGd5dWFnejNx</t>
+          <t>https://pf.kakao.com/_elwnn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1194,17 +1166,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5uzxl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>167</v>
+        <v>691</v>
       </c>
       <c r="Q8" t="n">
-        <v>152</v>
+        <v>1559</v>
       </c>
       <c r="R8" t="n">
-        <v>319</v>
+        <v>2250</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,47 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>12753889</t>
+          <t>1924109138</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12753889</t>
+          <t>https://m.place.naver.com/place/1924109138</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이펙스 화정점</t>
+          <t>헬로우짐 헬스&amp;PT 백석점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kimeunmi_o@naver.com</t>
+          <t>hellogym001@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1383-8244</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 화신로 263 브릿지타워 10층 전체호</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apex_gym_01</t>
+          <t>https://blog.naver.com/hellogym001</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,19 +1255,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ezo9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>641</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="n">
-        <v>507</v>
+        <v>220</v>
       </c>
       <c r="R9" t="n">
-        <v>1148</v>
+        <v>320</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1298459844</t>
+          <t>1528105437</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1298459844</t>
+          <t>https://m.place.naver.com/place/1528105437</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이플러스짐 PT 중산점</t>
+          <t>가온 휘트니스 대화마을점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>aplusgym600@naver.com</t>
+          <t>gaonfitness_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-977-5755</t>
+          <t>031-919-6336</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+          <t>경기도 고양시 일산서구 송포로 35 2층 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym600/222983159417</t>
+          <t>https://www.instagram.com/gaon_fitness_1?igsh=cTNodWxqdGMycWYy</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,19 +1349,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w2t1k29</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>489</v>
+        <v>980</v>
       </c>
       <c r="Q10" t="n">
-        <v>740</v>
+        <v>368</v>
       </c>
       <c r="R10" t="n">
-        <v>1229</v>
+        <v>1348</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,115 +1384,6213 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1426431657</t>
+          <t>1693727202</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426431657</t>
+          <t>https://m.place.naver.com/place/1693727202</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>짐300</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>gym_300@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1376-6714</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 고양대로 666 지하1층 M111, 112, 114, 115호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>https://blog.naver.com/gym_300/224211731704</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>311</v>
+      </c>
+      <c r="R11" t="n">
+        <v>611</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1408702037</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1408702037</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>맥스아웃휘트니스 정발산점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>maxoutfitness_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1376-9699</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1261번길 19 호수광장빌딩 9층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxoutfitness__1/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1655</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>653</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2308</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>35287626</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35287626</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>풍산휘트니스&amp;기구필라테스</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>psfitness_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>031-976-6911</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 풍산프라자 3층 전체</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/psfitness_pilates</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>476</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>561</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1037</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>38425785</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38425785</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>제이앤제이 피트니스 헬스&amp;PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>likegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1314-9695</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 2층 제이앤제이 피트니스</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jnjfitness_madu</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>451</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>303</v>
+      </c>
+      <c r="R14" t="n">
+        <v>754</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1181142706</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181142706</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>readybody2@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1359-9680</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/readybody2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>679</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1058</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1737</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>776760797</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/776760797</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>프라임핏 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>primefit_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>031-962-2306</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/prime_fit1/?igshid=MWpldjY4Y3h2dDF4ag%3D%3D</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1126</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>289</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1415</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1328418362</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1328418362</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gymonelab@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1328-9681</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>196</v>
+      </c>
+      <c r="R17" t="n">
+        <v>297</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1767374434</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1767374434</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>베르만짐 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>qpfmaks02@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1349-2708</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhhtNn</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>669</v>
+      </c>
+      <c r="R18" t="n">
+        <v>992</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1722963960</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1722963960</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>maxoutfitness_3@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1378-6366</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxoutfitness__2/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1277</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>203</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1480</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1674766909</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674766909</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MTO 피트니스 PT 정발산점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jbsfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1467-8389</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jbsfitness</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>429</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>729</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1158</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1314564243</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1314564243</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>momentfit100@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1483-9679</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xkxdCus</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>583</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>842</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1425</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1147827351</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147827351</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>범휘트니스 풍동점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>bumfitness6@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1441-7530</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을1로 29-37 201호, 202호, 203호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bumfitness6/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>148</v>
+      </c>
+      <c r="R22" t="n">
+        <v>438</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1604516167</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1604516167</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>휘트니스바로 중산점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fitnessbaro@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1467-5222</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 67 아카메디건물 5층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/fitnessbaro</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>914</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>254</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1168</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1120920642</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1120920642</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 마두역점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>onfleekfitness1@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1367-9479</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 장백로 178 3층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onfleekfitness1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>512</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>190</v>
+      </c>
+      <c r="R24" t="n">
+        <v>702</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1196366994</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196366994</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>healthboy67@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1373-7656</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/healthboygym67</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>617</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>791</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1408</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1251452457</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251452457</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>범휘트니스 마두점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bummadu@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 328 지하층 101, 102, 103호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bumfitness.madu/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>108</v>
+      </c>
+      <c r="R26" t="n">
+        <v>491</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1200977920</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200977920</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>kann5555@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1396-3191</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://fitnesskann.com/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>2044</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>965</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3009</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1797149054</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1797149054</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>developfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1374-2418</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/developfitness</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>708</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1006</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1714</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1332252606</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332252606</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 주엽점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>onfleekfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1366-9479</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 7층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/13/bizes/1064744</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>172</v>
+      </c>
+      <c r="R29" t="n">
+        <v>438</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1142951221</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1142951221</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>에이플러스짐휘트니스센터 백마학원가점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>aplusgym500@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aplusgym500/223716202422</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>111</v>
+      </c>
+      <c r="R30" t="n">
+        <v>201</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2067321363</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067321363</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>식스틴 휘트니스</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sixteen_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 성석로 7 2층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>469</v>
+      </c>
+      <c r="R31" t="n">
+        <v>646</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1004973811</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1004973811</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 탄현제니스점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1458-0638</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=80</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>755</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>33</v>
+      </c>
+      <c r="R32" t="n">
+        <v>788</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2038926940</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038926940</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 마두점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>respect1333@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1335-1380</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/respect1333</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1376</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1393</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2769</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1420492815</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1420492815</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>인프라짐 PT 대화역헬스장</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>infragym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1331-5665</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/infragym1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>2461</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2034</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4495</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>11579499</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11579499</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>크로스핏 GK 일산 마두점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>la40012@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1310-9524</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 113 지하1층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/cfgkmd</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>419</v>
+      </c>
+      <c r="R35" t="n">
+        <v>685</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1085090977</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1085090977</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>플렉스짐 백석점 PT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>flexgym_baekseok@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1361-3798</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/flexgym_baekseok</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>334</v>
+      </c>
+      <c r="R36" t="n">
+        <v>565</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1742139437</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742139437</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>플렉스짐</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>flexgymilsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1401-3798</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 고봉로 32-19 남정씨티프라자7차 2층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/flexgym_ilsan</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>870</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1193</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>36615589</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36615589</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>크로스핏 로얄 덕이점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cfroyal@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1313-5230</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 덕이로 328-12 1층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sEr5lrYd</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>206</v>
+      </c>
+      <c r="R38" t="n">
+        <v>225</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1498701834</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1498701834</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>actgym_02@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1445-5805</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>443</v>
+      </c>
+      <c r="R39" t="n">
+        <v>689</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1033726767</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1033726767</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>리와인드 휘트니스 중산점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>rewind_8990@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1300-9146</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rewind_fitness2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>138</v>
+      </c>
+      <c r="R40" t="n">
+        <v>305</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1726802714</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726802714</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>lifetime1231@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1355-9897</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lifetime1231/223007274910</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>492</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1140</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1632</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1618140538</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618140538</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>소녀감성핏 피티 PT/헬스 풍동점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>trainer_jey@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1417-9680</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 20 6층 소녀감성핏</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trainer_jey</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>359</v>
+      </c>
+      <c r="R42" t="n">
+        <v>498</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1544383388</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1544383388</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kann666@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1428-1174</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://fitnesskann.com/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1185</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>799</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1984</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1533278650</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1533278650</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>용구의 바디스토리</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>crazynael@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1461-9590</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-21 2층 204호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>25</v>
+      </c>
+      <c r="R44" t="n">
+        <v>51</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>21608242</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21608242</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>크로스핏ATD</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bebetters@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1352-5696</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주화로 210 우리프라자 B1</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/cfatd</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>46</v>
+      </c>
+      <c r="R45" t="n">
+        <v>62</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1758813134</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758813134</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>테디케이짐 헬스 PT 풍동점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>imka121@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1483-6336</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/imka121</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>257</v>
+      </c>
+      <c r="R46" t="n">
+        <v>798</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1011101134</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011101134</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 백마역점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>onfleekfitness4@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1389-9498</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 경의로 315 지하1층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onfleekfitness4/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>122</v>
+      </c>
+      <c r="R47" t="n">
+        <v>442</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1691525809</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691525809</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/5150fitness2</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>1225</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1611</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2836</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1817673935</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817673935</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>메인 휘트니스 후곡점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>main2211@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1484-2212</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 529 대화프라자 B동 지하1층 메인 휘트니스</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/main2211</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>288</v>
+      </c>
+      <c r="R49" t="n">
+        <v>488</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1308136724</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1308136724</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 일산역점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>onfleek555@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1319-9498</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 경의로 665 501호, 502호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onfleek555</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>158</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>140</v>
+      </c>
+      <c r="R50" t="n">
+        <v>298</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1112352231</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1112352231</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>툭짐</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ksm19088@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1313-1590</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1195 지1층 비101호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/took.gym</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>6</v>
+      </c>
+      <c r="R51" t="n">
+        <v>219</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2042000567</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2042000567</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>fitnessel_kintex@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1435-6332</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessel_kintex</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>315</v>
+      </c>
+      <c r="R52" t="n">
+        <v>520</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1678529668</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1678529668</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 탄현점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1321-3912</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 65 동현빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fpeoplew1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>904</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1217</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2121</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1845503473</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845503473</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>케이불스휘트니스 대화역점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>baik7479@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1418-9688</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 762 대화빌딩 4층 케이불스휘트니스 대화역점</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/baik7479</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>167</v>
+      </c>
+      <c r="R54" t="n">
+        <v>470</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>38251562</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38251562</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>F45 일산</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>f45_ilsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 2층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/f45_ilsan</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>232</v>
+      </c>
+      <c r="R55" t="n">
+        <v>353</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1034749202</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034749202</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>가온휘트니스 가좌 2호점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gaonfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1358-8077</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 송포로 261 101호 201호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gaonfitness2</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>259</v>
+      </c>
+      <c r="R56" t="n">
+        <v>340</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1261817011</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261817011</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 백석점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>respect9696@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1431-9696</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/respectgym3</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>287</v>
+      </c>
+      <c r="R57" t="n">
+        <v>497</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1412423288</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412423288</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>온플릭휘트니스 대화점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>onfleek_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1382-6682</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1573 킨텍스프라자 9층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onfleek_fitness_/?igshid=MmIzYWVlNDQ5Yg%3D%3D</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>325</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>326</v>
+      </c>
+      <c r="R58" t="n">
+        <v>651</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1050985755</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1050985755</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>디노짐 헬스PT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dinogym2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1341-5664</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dinogym2023</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>448</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>252</v>
+      </c>
+      <c r="R59" t="n">
+        <v>700</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1693675710</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693675710</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>크로스핏손오공 식사점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>lonelylight@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1390-3468</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 동국로 103 1층 크로스핏손오공</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/crossfits505</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>79</v>
+      </c>
+      <c r="R60" t="n">
+        <v>153</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1684777027</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1684777027</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>백석PT 짐플러스 휘트니스</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gymplus_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1370-0474</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1048 지하1층 짐플러스휘트니스</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymplus_fitness</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>67</v>
+      </c>
+      <c r="R61" t="n">
+        <v>147</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>38510579</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38510579</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>메인 휘트니스 백마학원가점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>main_bacma@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1489-2272</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강촌로 157 서울코아 비층 비01호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/main_bacma</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>156</v>
+      </c>
+      <c r="R62" t="n">
+        <v>341</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1057482007</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057482007</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>resort_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1434-4080</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/resort_13</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>563</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>908</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1471</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1379874016</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379874016</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>더스카이짐 중산마을점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>theskygym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1388-0593</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 탄중로 421 웅산프라자 지하1층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/theskygym3</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>318</v>
+      </c>
+      <c r="R64" t="n">
+        <v>414</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1519762125</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1519762125</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>더블에잇휘트니스덕이점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>double79988@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1346-7998</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 하이파크2로 40 금문프라자 7층 더블에잇휘트니스 덕이점</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/double79988</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>633</v>
+      </c>
+      <c r="R65" t="n">
+        <v>899</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1097065429</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1097065429</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>스포애니 마두역점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>spoany64@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1369-7697</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany64</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2221</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2709</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1639489562</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639489562</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>원잇핏 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>oneitfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1400-8861</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/oneitfit</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>596</v>
+      </c>
+      <c r="R67" t="n">
+        <v>825</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>13223584</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13223584</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>더블에잇휘트니스 마두점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>double7998@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1350-7998</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1171 현대프리젠트 9,10층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://partner.talk.naver.com/web/accounts/101675659/chat</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>733</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1020</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1951351429</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1951351429</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5150피트니스 중산점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>5150fitness5@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1370-4847</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 241 해태쇼핑타운 B1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/5150fitness5</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>408</v>
+      </c>
+      <c r="R69" t="n">
+        <v>757</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2006347781</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2006347781</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>saray78@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1431-9036</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/forestgym_2</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yfab</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>858</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>539</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1397</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1320621577</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320621577</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>버클다운짐 탄현점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>buckledown1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1358-3972</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1256</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1092</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2348</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1918164834</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1918164834</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>투게더휘트니스 일산점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>togetherfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1461-1485</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1356</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1358</v>
+      </c>
+      <c r="Q72" t="n">
         <v>350</v>
       </c>
-      <c r="R11" t="n">
-        <v>1706</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="R72" t="n">
+        <v>1708</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
         <is>
           <t>1161506645</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>더핏퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sky_se@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1411-0772</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sky_se/223038038455</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1134</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1315</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1707178271</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707178271</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>저스트플레잉</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>justplaying@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>031-965-1106</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://justplaying.co.kr/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>408</v>
+      </c>
+      <c r="R74" t="n">
+        <v>535</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>37452748</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37452748</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>bodyoffgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1381-8260</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyoffgym</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>510</v>
+      </c>
+      <c r="R75" t="n">
+        <v>643</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>32507674</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32507674</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>헌드레드짐 파주운정점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>hundredgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1327-5413</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/donghyeok_hundredgym/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>530</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>203</v>
+      </c>
+      <c r="R76" t="n">
+        <v>733</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1101743632</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101743632</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
